--- a/Data/noticias_piura_20260903_20260910.xlsx
+++ b/Data/noticias_piura_20260903_20260910.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,24 +495,24 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Comerciantes del Complejo de Mercados de Piura solicitan administración de parqueos</t>
+          <t>¿Quién responde por los 106 muertos en la región Piura? Nuevo asesinato se consuma en Castilla</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>A través de Resolución de Alcaldía N° 0592-2026, la Municipalidad Provincial de Piura ha dispuesto la conformación de una Comisión técnica multidisciplinaria para que evalué la viabilidad jurídica, técnica, económica, financiera, patrimonial y administrativa sobre la propuesta presentada por la Asociación regional de mercados de Piura (AREMEPI) referente a la administración de los estacionamientos del Complejo de Mercados. La asociación, que representa a los mercados formales, plantea implementar un modelo de gestión conjunta con la comuna piurana orientado a mejorar la administración del servicio, reducir los costos operativos y generar recursos económicos destinados a financiar proyectos estratégicos para el ordenamiento urbano del propio centro de abastos de la ciudad. La gerente de Desarrollo Económico, Ruth Oliva, señaló que hay voluntad política para evaluar el pedido de los comerciantes, por lo que se tendrá que esperar los informes técnicos para la toma de decisiones. REVERSIÓN La funcionaria también dio a conocer que realizaron una inspección en el Mercado San Miguel y constataron una vez más que varios puestos se encuentran cerrados. Indicó que este tipo de acciones que vienen realizando permitirán identificar los puestos que no cumplen con las disposiciones establecidas y, posteriormente, iniciar el proceso de reversión de aquellos espacios que correspondan, con el objetivo de brindar la oportunidad a otros comerciantes que sí tengan la voluntad de trabajar en dicho local comercial.</t>
+          <t>La racha criminal sigue en aumento en la región, luego que un joven técnico de celulares fuera asesinado de tres balazos en la cabeza y rostro por un gatillero, que disparó con una pasmosa frialdad, delante de dos amigos, para luego huir en un auto blanco. El asesinato de José Fernando Castillo Quevedo, de 24 años, ocurrió cerca de las nueve de la noche del pasado martes frente al bar “Pikaflor”, ubicado en la Asociación Villa Universitaria, sector norteste de Castilla. Hasta ese lugar llegó la Policía para iniciar las investigaciones. ESCALOFRIANTE DATA Con este episodio escaló a 106 los asesinatos ocurridos en lo que va del año en la región, siendo la mayoría de casos por la modalidad de sicariato (o crimenes por encargo). Cabe resaltar que en 2025 se registraron 107 homicidios en el lapso de enero a setiembre. Cabe precisar que en menos de 72 horas han ocurrido siete homicidios: dos mujeres, un varón y un menor de 13 años en Sullana, otro caso en Talara. De igual manera uno en Paita Alta y el último registrado en Castilla, contra José Fernando Castillo. IMÁGENES CLAVES El asesinato del joven técnico de equipos móviles muestra el alto grado de peligrosidad que existe en las calles. Precisamente una cámara de seguridad muestra que ya no se puede confian en nadie, luego que en escena se observa a José Fernando Castillo platicando con dos personas, que serían amigos. Según las imágenes de las cámaras de seguridad, Castillo Quevedo y dos sujetos, en la vía públlica, observan un celular. De pronto, se aprecia la salida de un individuo desconocido para subir apuradamente a un automóvil blanco y dar arranque. TODOS SE CONOCÍAN En ese momento, se oberva la llegada de un gatillero que vestía polo verde y bermuda blu jeans, quien se acerca a los tres amigos y dispara tres veces contra José Fernando Castillo, luego con pistola en mano camina y sube al mencionado vehículo blanco. Del mismo modo se distingue que uno de los dos individuos, que estaba conversando con la víctima mortal abordó el mismo vehículo en el que huyó el atacante. La Policía continúa con las investigaciones para esclarecer el crimen, identificar a los involucrados y determinar las circunstancias del asesinato.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/comerciantes-del-complejo-de-mercados-de-piura-solicitan-administracion-de-parqueos/</t>
+          <t>https://eltiempo.pe/local/quien-responde-por-los-106-muertos-en-la-region-piura-nuevo-asesinato-se-consuma-en-castilla/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>Andina</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -520,35 +520,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Burocracia retrasa obras de emergencia por el Fenómeno El Niño</t>
+          <t>Áncash: turista francés desaparece tras realizar vuelo en parapente desde nevado Alpamayo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>Mientras que entidades oficiales como Enfen y Senamhi advierten de un Fenómeno El Niño de “magnitud fuerte” o “extraordinario”; el empresariado piurano aún sigue a la espera que Proinversión defina los proyectos que se van ejecutar a través de la modalidad de “servicios por impuestos”. Se trata de 18 propuestas que han hecho llegar a Proinversión, según lo informó la gerente general de la Cámara de Comercio y Producción de Piura, Susana Seminario, quien ayer aprovechó la presencia de los ministros de Desarrollo Agrario y Riego, Marco Vinelli; del ministro de Defensa, Rafael Belaúnde Llosa y de otras autoridades que participaron de la reunión de trabajo de la Plataforma de Defensa Civil para pedir celeridad en los trámites y los proyectos se pueden iniciar cuanto antes en aras de mitigar el impacto del FEN. S/ 130 millones La empresaria también dio a conocer que disponen de 130 millones de soles en impuestos para ser ejecutados en los proyectos de emergencia. Chutuque La ampliación del canal de Chutuque es una de las prioridades de los empresarios para evitar una posible inundación. Mientras días atrás el presidente de la Camco, Javier Bereche, señalaba que se trata de “un canal de 6.7 kilómetros de roca y eso hay que volarlo”, ayer el titular del Midagri remarcó que dentro de dos o tres días se iniciarán los trabajos, pero solo limpiarán 5 kilómetros que iniciarán en el distrito de Cristo Nos Valga y terminarán en Sechura. “Es lo que se puede garantizar y cumplir”, subrayó. Bajo Piura Sobre el reclamo del Bajo Piura que demanda más maquinaria para los trabajos de descolmatación, el ministro Vinelli aseguró que en los próximos días llegará más maquinaria aguas abajo del puente Grau. Para 3,900 m3/s Vinelli también dio a conocer que los trabajos de descolmatación tienen un avance del 42% en el tramo entre la represa Los Ejidos y el puente Bolognesi y el objetivo es ampliar la capacidad de la caja hidráulica a 3.900 metros cúbicos por segundo (m3/s); sin embargo, el supervisor de los trabajos indicó un día antes que la proyección es para 3.000 m3/s. Ayuda humanitaria Finalmente se dio a conocer que actualmente se cuenta con 725 toneladas de ayuda humanitaria en el almacén central y 113 toneladas distribuidas en 17 almacenes adelantados, además de 51 motobombas en mantenimiento y la planificación para incorporar otras 70. Solo priorizan 69 establecimientos de salud Durante la reunión realizada en el Gobierno Regional, también se dio a conocer sobre la intervención de establecimientos de salud para mitigar el impacto del FEN. Sin embargo, se informó que de los 438 establecimientos de salud existentes en la región, 269 requieren algún tipo de intervención y se han priorizado 69. Asimismo, se informó sobre la coordinación para implementar un hospital temporal de 104 camas en la Universidad de Piura, además del fortalecimiento de brigadas, equipos de fumigación, ambulancias y acciones de prevención frente al dengue. Sobre las vacunas, el titular del Midagri aseguró que llegará otro lote de 50 mil vacunas contra el dengue.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/burocracia-retrasa-obras-de-emergencia-por-el-fenomeno-el-nino/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Andina</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Áncash: turista francés desaparece tras realizar vuelo en parapente desde nevado Alpamayo</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
         <is>
           <t>El extranjero fue identificado como Pierre Jacky Marc, de 27 años, quien realizó el descenso en parapente junto con su compatriota Thomas Max Michel, de 31 años, desde una altitud cercana a los 6,000 metros sobre el nivel del mar.
 De acuerdo con información preliminar, Marc habría sufrido un accidente durante el descenso y desde entonces se desconoce su paradero .
@@ -563,27 +538,27 @@
 ?? https://t.co/XVzLfqz0RJ pic.twitter.com/gNsC9qLuwJ — Agencia Andina (@Agencia_Andina) September 10, 2026</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-ancash-turista-frances-desaparece-tras-realizar-vuelo-parapente-desde-nevado-alpamayo-1091201.aspx</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Andina</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B5" s="2" t="n">
         <v>46275</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Proyecto educativo "La página oculta" visibiliza líderes afrodecescendientes</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Lee también: ["Presentan libro sobre el legado artístico de Alberto Guzmán"] A partir de una investigación liderada por la historiadora Maribel Arrelucea y el uso de referencias históricas y familiares, el equipo creativo logró recrear los rostros y trayectorias de cuatro figuras clave: Alberto "Grumete" Medina, héroe de la Guerra del Pacífico; Catalina Buendía de Pecho, lideresa de la resistencia en Ica; Francisco Congo, fundador del Palenque Huachipa; e Ildefonso, combatiente de la causa independentista.
 Los materiales impresos han sido diseñados e insertados estratégicamente para complementar los textos escolares existentes.
@@ -595,9 +570,82 @@
 Más en Andina La Municipalidad de Lima, a través de la Gerencia de Cultura, presenta la exposición “Francisco González Gamarra: tres miradas en la acuarela”, una muestra que permite redescubrir la versatilidad de uno de los más importantes artistas peruanos del siglo XX… pic.twitter.com/BjzoBExNkt — Agencia Andina (@Agencia_Andina) September 9, 2026</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-proyecto-educativo-pagina-oculta-visibiliza-lideres-afrodecescendientes-1091206.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fenómeno El Niño: arribo de otras cuatro ondas Kelvin vigorizarán el calentamiento del mar</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>En declaraciones a la Agencia Andina , el también vocero del Instituto del Mar del Perú (IMARPE) precisó que las estaciones de esta institución registraron en Piura una anomalía de hasta 7.4 °C por encima de su temperatura habitual para esta época.
+Sostuvo que estas anomalías en la temperatura del litoral se explican por la presencia de dos ondas Kelvin que arribaron al mar peruano a fines de agosto y en los primeros días de septiembre y eso está contribuyendo al incremento de la temperatura del mar.
+Luis Vásquez afirmó que en las siguientes semanas arribarán otras ondas Kelvin.
+"Entre septiembre y noviembre arribarán cuatro onda Kelvin , entonces eso también genera el calentamiento que se viene dando frente a la costa peruana”, explicó Vásquez a la Agencia Andina .
+El especialista explicó que este calentamiento se refleja en las anomalías registradas en diferentes puntos del litoral, aunque con intensidades distintas según la zona.
+La mayor anomalía se presenta actualmente frente a Paita, con 7.4 °C por encima de su promedio habitual.
+De acuerdo con el especialista, e n San José la anomalía alcanza 5.2 °C, mientras que en Tumbes llega a 3.3 °C.
+"Estos valores muestran que el calentamiento no es uniforme a lo largo del litoral", subrayó.
+Paita registra la mayor anomalía Vásquez precisó que las anomalías deben diferenciarse de la temperatura absoluta registrada en cada localidad.
+Por ejemplo, en Paita se registró una temperatura de alrededor de 24 °C , pero debido a que este valor está muy por encima de lo habitual para esa zona, representa una anomalía de 7.4 °C.
+En cambio, en Tumbes la temperatura llegó a 28.5 °C, pero la anomalía fue de 3.3 °C.
+En Ilo, en el sur del litoral, se registró una temperatura absoluta de 19.1 °C, que representó una anomalía de 4.4 °C.
+“Hay una variabilidad de valores absolutos de norte a sur y no necesariamente significa que la mayor temperatura es una mayor anomalía”, explicó.
+El calentamiento no será permanente El vocero de IMARPE indicó que el efecto de una onda Kelvin puede generar un incremento de la temperatura , pero posteriormente esta puede disminuir parcialmente.
+“Pasa el efecto de la onda Kelvin y vuelve a disminuir un poco, pero no van a pasar a una condición normal”, sostuvo.
+Por ello, las actuales temperaturas elevadas no necesariamente se mantendrán durante todo el mes.
+La variabilidad diaria y el desplazamiento de las ondas hacen necesario analizar los valores mediante promedios.
+Vásquez recordó que mientras los boletines pueden mostrar temperaturas promedio diarias, índices como el ICEN se calculan sobre la base de promedios mensuales, precisamente para evitar que las fluctuaciones de un día determinado determinen por sí solas la categoría climática.
+Cuatro nuevas ondas Kelvin se dirigen hacia la costa El calentamiento podría prolongarse debido a que no solo están actuando las ondas Kelvin que ya arribaron.
+Vásquez remarcó que otras cuatro ondas Kelvin se encuentran actualmente en tránsito y se espera que lleguen entre setiembre y noviembre.
+Estas nuevas ondas podrían contribuir a mantener las condiciones cálidas frente al litoral peruano y favorecer la evolución hacia una condición más intensa de El Niño Costero .
+“ Eso condiciona que el mar se va a mantener caliente y puede contribuir a pasar justamente a la condición extraordinaria”, afirmó.
+Pese a las elevadas anomalías observadas en varios puntos del litoral, Vásquez remarcó que todavía no se puede afirmar que el fenómeno haya ingresado a la condición extraordinaria.
+Explicó que las condiciones actuales contribuyen al tránsito hacia esa categoría, pero la clasificación depende del comportamiento de las temperaturas durante todo el mes.
+“Todavía no ha pasado el mes.
+Tenemos nueve días del mes y día a día varía la temperatura y va a variar la anomalía”, señaló.
+De acuerdo con el especialista, para que el ICEN determine una condición extraordinaria, el promedio mensual de las anomalías en la región Niño 1+2 debe superar los 3.5 °C.
+Por ello, un registro excepcional de temperatura durante determinados días no basta por sí solo para establecer la categoría del fenómeno.
+Núcleo de agua cálida alcanza anomalías de hasta 6 °C El calentamiento también se mantiene en la profundidad del mar.
+Vásquez señaló que existe una condición cálida que se extiende aproximadamente hasta los 150-200 metros de profundidad, con anomalías cercanas a 2 °C respecto de los valores normales.
+Recordó que durante junio y julio se llegaron a registrar anomalías de hasta 8 °C en algunos sectores .
+Aunque posteriormente disminuyeron, todavía persiste un núcleo cálido con anomalías de hasta 6 °C, aproximadamente a 50 metros de profundidad.
+Este contenido de calor en el océano constituye uno de los elementos que IMARPE mantiene bajo vigilancia ante la evolución del actual escenario cálido.
+Temperaturas superiores a 26 °C pueden favorecer más humedad Respecto a la posibilidad de que el calentamiento del mar incremente las lluvias durante el próximo verano , Vásquez explicó que existe una relación entre las temperaturas superficiales elevadas y una mayor evaporación y aporte de humedad a la atmósfera .
+El especialista indicó que cuando las temperaturas absolutas cercanas al litoral alcanzan aproximadamente 26 a 27 °C, el aporte de humedad puede adquirir mayor importancia y asociarse más directamente con las precipitaciones.
+Sin embargo, precisó que el contexto estacional es determinante.
+Actualmente, el país todavía atraviesa una época relativamente seca, por lo que un incremento de la humedad y las temperaturas del mar no necesariamente generaría precipitaciones significativas de inmediato.
+El escenario cambia hacia noviembre, cuando comienza a aumentar la precipitación, y especialmente durante el verano, cuando el riesgo de lluvias intensas es mayor.
+Febrero y marzo concentran el mayor riesgo El especialista señaló que el mayor riesgo se presenta durante los meses de febrero y marzo, periodo en el que normalmente se concentra una mayor cantidad de precipitaciones.
+En ese contexto, la combinación de temperaturas cálidas del mar, mayor humedad atmosférica y precipitaciones propias de la temporada podría incrementar el riesgo de desbordes de ríos, inundaciones y huaicos, principalmente en las zonas más vulnerables.
+No obstante, destacó que las acciones de prevención y reducción del riesgo pueden contribuir a disminuir los impactos sobre la población y las actividades económicas.
+Norte concentra temperaturas más elevadas, pero calentamiento alcanza otras zonas Aunque las mayores temperaturas absolutas se observan en el litoral norte, Vásquez aclaró que las anomalías positivas no se limitan exclusivamente a esa zona.
+La diferencia radica en que cada localidad tiene un valor climático normal distinto.
+Por ello, una temperatura de 24 °C puede representar una anomalía mucho mayor en Paita que una temperatura de 28.5 °C en Tumbes.
+El seguimiento de ambos indicadores —temperatura absoluta y anomalía respecto al promedio— resulta fundamental para evaluar la evolución del calentamiento y sus posibles efectos sobre el clima.
+Para IMARPE, el comportamiento de las próximas semanas será determinante, especialmente considerando que cuatro nuevas ondas Kelvin podrían arribar entre setiembre y noviembre, manteniendo el contenido de calor del océano y favoreciendo la persistencia de condiciones cálidas frente a la costa peruana.
+Más en Andina: ???? Sheyla Méndez y ‘Traveleras’ llevan 10 años promoviendo destinos y cultura peruana en redes.
+Hoy son parte de ‘Más peruano que nunca’, campaña por los 15 años de Marca Perú.
+?? https://t.co/eSiowiilxM pic.twitter.com/KKeJBB62in — Agencia Andina (@Agencia_Andina) September 10, 2026</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-proyecto-educativo-pagina-oculta-visibiliza-lideres-afrodecescendientes-1091206.aspx</t>
+          <t>https://andina.pe/agencia/noticia-fenomeno-nino-arribo-otras-cuatro-ondas-kelvin-vigorizaran-calentamiento-del-mar-1091215.aspx</t>
         </is>
       </c>
     </row>
@@ -612,10 +660,40 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>Visita de Marco Rubio muestra relevancia del Perú para los Estados Unidos, destacan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Como se recuerda, la autoridad norteamericana cumple una visita oficial a nuestro país que incluyó reuniones con el canciller Carlos Espá y la presidenta de la república, Keiko Fujimori.
+"Siempre es positiva esta visita, que venga al Perú el secretario de Estado de los Estados Unidos también muestra la relevancia del país para Estados Unidos en el análisis geopolítico y global", afirmó a Exitosa.
+En ese sentido, indicó que será necesario aprovechar este momento y esta visita para seguir fortaleciendo nuestras relaciones con los Estados Unidos.
+Sobre el anuncio de la incorporación del Perú al Escudo de las Américas , manifestó que se trata de una buena oportunidad para nuestro país.
+" Significa tener apoyo de inteligencia y logística porque vivimos una situación de inseguridad muy fuerte y Estados Unidos nos puede apoyar para tener resultados más rápidos", refirió.
+Asimismo, dijo que en el apoyo al Perú en acciones ante la presencia del fenómeno El Niño será importante porque el país norteamericano cuenta con una logística muy grande, incluso anunciaron la llegada del buque - hospital a la costa de Piura.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://andina.pe/agencia/noticia-visita-marco-rubio-muestra-relevancia-del-peru-para-los-estados-unidos-destacan-1091219.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Andina</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>Fenómeno El Niño: intensifican trabajos en el río Piura para reducir riesgo de desbordes</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Así lo informó la ANA que precisó que la intervención preventiva busca reducir el riesgo de desbordes y disminuir la vulnerabilidad de 30 familias y aproximadamente 80 hectáreas de cultivos permanentes de mango, limón y cacao, ubicados en zonas próximas al cauce.
 Para acelerar las labores, el equipo técnico de la Meta 246 de la ANA desplegó cinco maquinarias pesadas (tres tractores D-8 y dos excavadoras), que operan durante jornadas diurnas y nocturnas.
@@ -632,95 +710,59 @@
 ?? https://t.co/B9YXZPQPnL ?? Moisés Aylas Ortiz pic.twitter.com/jIKWZuvta3 — Agencia Andina (@Agencia_Andina) September 10, 2026</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://andina.pe/agencia/noticia-fenomeno-nino-intensifican-trabajos-el-rio-piura-para-reducir-riesgo-desbordes-1091232.aspx</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>El Tiempo</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>46275</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>¿Quién responde por los 106 muertos en la región Piura? Nuevo asesinato se consuma en Castilla</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>La racha criminal sigue en aumento en la región, luego que un joven técnico de celulares fuera asesinado de tres balazos en la cabeza y rostro por un gatillero, que disparó con una pasmosa frialdad, delante de dos amigos, para luego huir en un auto blanco. El asesinato de José Fernando Castillo Quevedo, de 24 años, ocurrió cerca de las nueve de la noche del pasado martes frente al bar “Pikaflor”, ubicado en la Asociación Villa Universitaria, sector norteste de Castilla. Hasta ese lugar llegó la Policía para iniciar las investigaciones. ESCALOFRIANTE DATA Con este episodio escaló a 106 los asesinatos ocurridos en lo que va del año en la región, siendo la mayoría de casos por la modalidad de sicariato (o crimenes por encargo). Cabe resaltar que en 2025 se registraron 107 homicidios en el lapso de enero a setiembre. Cabe precisar que en menos de 72 horas han ocurrido siete homicidios: dos mujeres, un varón y un menor de 13 años en Sullana, otro caso en Talara. De igual manera uno en Paita Alta y el último registrado en Castilla, contra José Fernando Castillo. IMÁGENES CLAVES El asesinato del joven técnico de equipos móviles muestra el alto grado de peligrosidad que existe en las calles. Precisamente una cámara de seguridad muestra que ya no se puede confian en nadie, luego que en escena se observa a José Fernando Castillo platicando con dos personas, que serían amigos. Según las imágenes de las cámaras de seguridad, Castillo Quevedo y dos sujetos, en la vía públlica, observan un celular. De pronto, se aprecia la salida de un individuo desconocido para subir apuradamente a un automóvil blanco y dar arranque. TODOS SE CONOCÍAN En ese momento, se oberva la llegada de un gatillero que vestía polo verde y bermuda blu jeans, quien se acerca a los tres amigos y dispara tres veces contra José Fernando Castillo, luego con pistola en mano camina y sube al mencionado vehículo blanco. Del mismo modo se distingue que uno de los dos individuos, que estaba conversando con la víctima mortal abordó el mismo vehículo en el que huyó el atacante. La Policía continúa con las investigaciones para esclarecer el crimen, identificar a los involucrados y determinar las circunstancias del asesinato.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://eltiempo.pe/local/quien-responde-por-los-106-muertos-en-la-region-piura-nuevo-asesinato-se-consuma-en-castilla/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>El Tiempo</t>
+          <t>El Comercio</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Advierten que la sensación del calor podría llegar a los 39°C en la región Piura</t>
+          <t>¿Masificación de gas en el norte? Gasoducto entre Piura y Chiclayo es posible, señala Gas Energy</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>El Senamhi Piura informó que durante el mes, se registraron temperaturas de hasta 37,2°C en Chulucanas, Piura. No descartan que la sensación de calor pueda alcanzar los 39 °C en Piura. Así lo señaló el especialista del Senamhi Piura, Héctor Yauri quien indicó que este panorama se podría dar por diversos factores, con lo cual la población deberá tomar sus precauciones. El Senamhi informó que durante las últimas semanas las temperaturas se han mantenido por encima de sus valores normales, especialmente las temperaturas máximas. MAGNITUD FUERTE Explican que esta situación estaría “asociada principalmente a la persistencia de anomalías positivas de la temperatura superficial del mar frente a la costa de Piura y en la región Niño 1+2”. “Se espera que las temperaturas del aire continúen registrando valores relativamente elevados durante las próximas semanas, debido a la persistencia de temperaturas superficiales del mar por encima de lo normal en la región Niño 1+2. Estas condiciones son consistentes con la evolución del evento Niño Costero, que actualmente presenta magnitud fuerte, favoreciendo la persistencia de temperaturas superiores a los valores climatológicos para la temporada”, indicó el especialista Fabricio Fabián Herrera. Asimismo, de acuerdo al aviso meteorológico 161 del Senamhi, no se descarta lluvias dispersas en la costa norte y la presencia de lluvias localizadas en la sierra norte.</t>
+          <t>El norte del Perú tiene la oportunidad de abastecerse de gas natural y lograr una verdadera masificación sin la obligatoriedad de recurrir a Camisea. Esto, a través de la construcción de gasoductos que aprovechen el potencial de los lotes de hidrocarburos piuranos. Y es que la única manera de lograr un proceso de masificación económico y eficiente es “construyendo tubos”, alternativa que elimina la necesidad de transportar el gas en camiones, apunta Luis Fernández, socio director de Gas Energy Perú. En esa línea, la consultora lanzó en la XV Conferencia Gas Natural Perú 2026 una propuesta para crear un corredor energético de gas natural entre Piura y Chimbote utilizando las reservas y recursos de los campos piuranos, hoy desaprovechados. “El norte del Perú tiene suficientes reservas y recursos para crear un polo de desarrollo energético e industrial descentralizado e independiente del gas de Camisea”, manifiesta el especialista. Así, la consultora propone construir un gasoducto de 250 kilómetros de longitud que conecte Piura con la localidad lambayecana de Eten, en una primera etapa, sacando partido de la existencia de dos plantas térmicas en esa jurisdicción, las cuales servirán de ‘ancla’ para el proyecto. Es el caso de las centrales duales Eten (180 MW) y Recka (190 MW) las cuales están en capacidad de producir electricidad tanto con gas como con diésel. Se trata, explica Fernández, de dos infraestructuras que hoy en día no pueden ser abastecidas con gas pues el transporte en camiones cisternas no permite el abastecimiento de grandes volúmenes. De allí la solución de un gasoducto capaz de proveer los 80 millones de pies cúbicos diarios (mmpcd) de gas que necesitarían continuamente. “Si tenemos 80 mmpcd de demanda en Éten ya existiría un ancla para incentivar la producción de los lotes piuranos. Y a ello se agregaría la demanda de GNV en Chiclayo y las azucareras que tienen un alto consumo de energía”, precisa el especialista. Piura produce y consume alrededor de 60 mmpcd de gas natural. La apertura de nuevos mercados en Lambayeque incentivaría la búsqueda y producción de mayores volúmenes, lo cual no representaría un problema pues la región tiene un potencial de 5,5 trillones de pies cúbicos (TFC) de gas, es decir, 91.666 veces su producción diaria hoy. “Conceptualmente, el proyecto es posible porque existe el gas y existen las centrales térmicas que servirían de ancla. Por lo tanto, se puede construir la infraestructura”, manifiesta Fernández. Dicho ducto recorrería Paita, Sechura y Bayóvar hasta llegar a Éten, siguiendo un recorrido paralelo al que Gasnorp opera en Piura. Así, se conectaría la ciudad de Chiclayo, en primer lugar, y luego las de Trujillo, Paramonga y Chimbote, andando el tiempo. Lo único que faltaría para concretar el proyecto es plasmar las condiciones para que sea comercial y regulatoriamente posible, anota Fernández. Y es que la regulación no contempla una tarifa especial para el sector de generación eléctrica en el norte del país, a diferencia de lo que ocurre en las concesiones de Lima (Cálidda) e Ica (Contugas). “Para que el proyecto tenga éxito hace falta armar una nueva regulación que permita que esas centrales entren en base y para ello se necesita políticas adecuadas que partan desde el Minem”, anota Fernández.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/advierten-que-la-sensacion-del-calor-podria-llegar-a-los-39c-en-la-region-piura/</t>
+          <t>https://elcomercio.pe/economia/peru/masificacion-de-gas-en-el-norte-gasoducto-entre-piura-y-chiclayo-es-posible-senala-gas-energy-noticia/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ballena jorobada de 14 metros de longitud fue varada en playa Sombrero Chico de Arequipa</t>
+          <t>Comerciantes del Complejo de Mercados de Piura solicitan administración de parqueos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>El evento fue atendido por personal especializado de la sede desconcentrada del Imarpe en Camaná .
-Como resultado de la inspección, se determinó que se trataba de un ejemplar adulto de ballena jorobada.
-Su aleta pectoral medía 3.2 metros y la aleta caudal 2.3 metros.
-El ejemplar presentaba un avanzado estado de descomposición, lo que imposibilitó la necropsia para determinar la causa de muerte.
-No obstante, se colectaron muestras de tejido, entre ellas de piel y aleta, para su posterior análisis .
-Debido al estado de descomposición, no fue posible determinar la presencia de marcas o lesiones que pudieran estar asociadas a una eventual interacción con actividades pesqueras.
-Las ballenas jorobadas realizan migraciones anuales desde sus zonas de alimentación hacia áreas de reproducción ubicadas en regiones tropicales y subtropicales durante el invierno austral.
-En este periodo, su presencia frente a la costa peruana es frecuente, principalmente entre mayo y noviembre, temporada en la que también puede incrementarse el riesgo de interacción con actividades pesqueras y otras actividades humanas.
-Lea también: Piura: Imarpe reporta varamiento de ballena jorobada juvenil en playa Colán El Imarpe continuará con el monitoreo de estos eventos con el propósito de generar información científica que contribuya a fortalecer el conocimiento y la conservación de los mamíferos marinos en el litoral peruano.
-Asimismo, el Imarpe recuerda a la ciudadanía que debe evitar el contacto directo con animales marinos varados, tanto vivos como muertos, debido al riesgo de exposición a agentes patógenos.
-Ante el hallazgo de un ejemplar, se recomienda comunicar el hecho a las autoridades competentes y mantener una distancia prudente mientras se realizan las evaluaciones correspondientes.
-Más en Andina: ?? Llegaron a Piura los dos primeros puentes modulares para atender emergencias por El Niño https://t.co/C8pc6YwjLi pic.twitter.com/42W8rND7VP — Agencia Andina (@Agencia_Andina) September 10, 2026</t>
+          <t>A través de Resolución de Alcaldía N° 0592-2026, la Municipalidad Provincial de Piura ha dispuesto la conformación de una Comisión técnica multidisciplinaria para que evalué la viabilidad jurídica, técnica, económica, financiera, patrimonial y administrativa sobre la propuesta presentada por la Asociación regional de mercados de Piura (AREMEPI) referente a la administración de los estacionamientos del Complejo de Mercados. La asociación, que representa a los mercados formales, plantea implementar un modelo de gestión conjunta con la comuna piurana orientado a mejorar la administración del servicio, reducir los costos operativos y generar recursos económicos destinados a financiar proyectos estratégicos para el ordenamiento urbano del propio centro de abastos de la ciudad. La gerente de Desarrollo Económico, Ruth Oliva, señaló que hay voluntad política para evaluar el pedido de los comerciantes, por lo que se tendrá que esperar los informes técnicos para la toma de decisiones. REVERSIÓN La funcionaria también dio a conocer que realizaron una inspección en el Mercado San Miguel y constataron una vez más que varios puestos se encuentran cerrados. Indicó que este tipo de acciones que vienen realizando permitirán identificar los puestos que no cumplen con las disposiciones establecidas y, posteriormente, iniciar el proceso de reversión de aquellos espacios que correspondan, con el objetivo de brindar la oportunidad a otros comerciantes que sí tengan la voluntad de trabajar en dicho local comercial.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-ballena-jorobada-14-metros-longitud-fue-varada-playa-sombrero-chico-arequipa-1091164.aspx</t>
+          <t>https://eltiempo.pe/local/comerciantes-del-complejo-de-mercados-de-piura-solicitan-administracion-de-parqueos/</t>
         </is>
       </c>
     </row>
@@ -731,28 +773,28 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bajo Piura se levanta y exige obras para evitar inundación</t>
+          <t>Burocracia retrasa obras de emergencia por el Fenómeno El Niño</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>La población no quiere ser expectante de como apenas siete maquinarias pesadas trabajan en la descolmatación del río Piura, desde el puente Grau hasta el puente Independencia, sin haberse considerado obras adicionales como el reforzamiento de las defensas ribereñas, los diques de contención, entre otras obras que permitan mitigar el impacto del Fenómeno El Niño (FEN) que se avecina. Por ello ayer, y tras una asamblea, dirigentes de los distritos de Catacaos, Cura Mori y El Tallán acordaron realizar una marcha de protesta el 14 de setiembre a partir de las 8:00 a.m. bajo el lema “Inundación nunca más”. La población está dispuesta a bloquear las vías hasta ser escuchados por las autoridades. «Es una burla» Víctor Chunga, presidente del Frente de reconstrucción de pueblos afectados por el Niño Costero 2017, calificó como una “burla” que en su primera visita a Piura la presidenta Keiko Fujimori anunciara una inversión de 140 millones y un pull de maquinaria para los trabajos de descolmatación y no se está cumpliendo. “Anunció 140 millones, luego 129 millones, pero no está desglosado cuánto le toca a Piura y los trabajos no van ni al 30%. Ahora en la descolmatación (hacia el Bajo Piura) solo están retirando 90 centímetros de sedimento, eso es limpieza no descolmatación”, indicó. Para octubre prometen terminar descolmatación Tras la denuncia del diputado Félix Chang Apuy, sobre la paralización de los trabajos de descolmatación del río Piura, el supervisor de estos trabajos, Ítalo Cuba, señaló que ya solucionaron el tema administrativo de los contratos del personal y se ha retomado los trabajos en el tramo entre la represa Los Ejidos y el puente Bolognesi. Informó que 20 maquinarias pesadas del Gobierno Regional se sumarán a los trabajos, con lo cual esperan culminar los mismos antes de las lluvias pronosticadas para noviembre. “A mediados de octubre se quiere terminar todo esto”, indicó el supervisor quien agregó que buscan recuperar un encausamiento del río con capacidad para 3000 m3/s.</t>
+          <t>Mientras que entidades oficiales como Enfen y Senamhi advierten de un Fenómeno El Niño de “magnitud fuerte” o “extraordinario”; el empresariado piurano aún sigue a la espera que Proinversión defina los proyectos que se van ejecutar a través de la modalidad de “servicios por impuestos”. Se trata de 18 propuestas que han hecho llegar a Proinversión, según lo informó la gerente general de la Cámara de Comercio y Producción de Piura, Susana Seminario, quien ayer aprovechó la presencia de los ministros de Desarrollo Agrario y Riego, Marco Vinelli; del ministro de Defensa, Rafael Belaúnde Llosa y de otras autoridades que participaron de la reunión de trabajo de la Plataforma de Defensa Civil para pedir celeridad en los trámites y los proyectos se pueden iniciar cuanto antes en aras de mitigar el impacto del FEN. S/ 130 millones La empresaria también dio a conocer que disponen de 130 millones de soles en impuestos para ser ejecutados en los proyectos de emergencia. Chutuque La ampliación del canal de Chutuque es una de las prioridades de los empresarios para evitar una posible inundación. Mientras días atrás el presidente de la Camco, Javier Bereche, señalaba que se trata de “un canal de 6.7 kilómetros de roca y eso hay que volarlo”, ayer el titular del Midagri remarcó que dentro de dos o tres días se iniciarán los trabajos, pero solo limpiarán 5 kilómetros que iniciarán en el distrito de Cristo Nos Valga y terminarán en Sechura. “Es lo que se puede garantizar y cumplir”, subrayó. Bajo Piura Sobre el reclamo del Bajo Piura que demanda más maquinaria para los trabajos de descolmatación, el ministro Vinelli aseguró que en los próximos días llegará más maquinaria aguas abajo del puente Grau. Para 3,900 m3/s Vinelli también dio a conocer que los trabajos de descolmatación tienen un avance del 42% en el tramo entre la represa Los Ejidos y el puente Bolognesi y el objetivo es ampliar la capacidad de la caja hidráulica a 3.900 metros cúbicos por segundo (m3/s); sin embargo, el supervisor de los trabajos indicó un día antes que la proyección es para 3.000 m3/s. Ayuda humanitaria Finalmente se dio a conocer que actualmente se cuenta con 725 toneladas de ayuda humanitaria en el almacén central y 113 toneladas distribuidas en 17 almacenes adelantados, además de 51 motobombas en mantenimiento y la planificación para incorporar otras 70. Solo priorizan 69 establecimientos de salud Durante la reunión realizada en el Gobierno Regional, también se dio a conocer sobre la intervención de establecimientos de salud para mitigar el impacto del FEN. Sin embargo, se informó que de los 438 establecimientos de salud existentes en la región, 269 requieren algún tipo de intervención y se han priorizado 69. Asimismo, se informó sobre la coordinación para implementar un hospital temporal de 104 camas en la Universidad de Piura, además del fortalecimiento de brigadas, equipos de fumigación, ambulancias y acciones de prevención frente al dengue. Sobre las vacunas, el titular del Midagri aseguró que llegará otro lote de 50 mil vacunas contra el dengue.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/bajo-piura-se-levanta-y-exige-obras-para-evitar-inundacion/</t>
+          <t>https://eltiempo.pe/local/burocracia-retrasa-obras-de-emergencia-por-el-fenomeno-el-nino/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Andina</t>
+          <t>El Tiempo</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -760,20 +802,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Llegaron a Piura los dos primeros puentes modulares para atender emergencias por El Niño</t>
+          <t>Dos gatilleros matan a sujeto y hieren a otro en Paita, pero Policía los captura</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Este traslado corresponde a una primera etapa de movilización de 25 puentes modulares metálicos hacia el norte, con destino a Tumbes, Piura y Lambayeque, y hacia el sur del país, principalmente a Ayacucho y Puno.
-Los puentes podrán ser trasladados e instalados en los puntos donde se produzcan daños en la infraestructura vial, facilitando la recuperación del tránsito y el desplazamiento de personas, alimentos, medicinas, maquinaria y otros productos esenciales.
-Lea también: Ministro de Defensa confía en avance del Ejército para recuperar cauce del río Piura Con esta estrategia, el MTC fortalece su capacidad operativa para responder oportunamente ante eventuales interrupciones de las vías nacionales y evitar que las emergencias generen aislamiento de las poblaciones o afecten el abastecimiento y las actividades económicas de las zonas comprometidas.
-Más en Andina: ???? La selva de doce regiones soportará los días 13 y 14 de setiembre lluvias, de ligera a moderada intensidad, así como descargas eléctricas, ráfagas de viento con velocidades cercanas a los 45 kilómetros por hora (km/h) y cobertura nubosa, debido al ingreso del décimo friaje,… pic.twitter.com/6a3ceAYojC — Agencia Andina (@Agencia_Andina) September 9, 2026</t>
+          <t>A cinco se incrementaron los asesinatos del pasado lunes en la región, luego que gatilleros motorizados asesinaran a tiros a joven en Paita alta y dejarán gravemente herido a su amigo. Esta vez, la Policía Nacional en rápida repuesta capturó a balazos dos sospechosos, incautando una motocicleta y un arma de fuego. Transcurría las 9:50 de la noche del lunes, cuando los amigos Giancarlo Jiménez Hernández, de 33 años, y William Daniel Aldana Prado, de 24 años, caminaban por la parte posterior de las empresas de transporte Andrea y Santangel, fueron interceptados por una motocicleta. Disparó a matar El sujeto que iba como pasajero sacó un arma de fuego y disparó a matar contra los dos amigos. Los ocupantes de la motocicleta al ver caer a sus blancos se dieron a la fuga por las calles de Paita Alta. Los dos amigos gravemenre heridos fueron socorridos y trasladados de emergencia al Hospital Nuestra Señora de las Mercedes.Lamentablemente, el médico de turno, Ricardo Pereira certificó la muerte de Giancarlo Jiménez por hemorragia intercraneal por disparo de arma de fuego. En tanto, dio el diagnóstico oara Willian Aldaba de traumatismo abdominal abierto por proyectil con arma de fuego. Su estado de salud es de pronostico reservado. Persecución y captura Un grupo de agentes de la Comisaría Ciudad del Pescador con las características de la moto y los sujetos a inmediaciones del colegio “Lunitas de Paita” localizó la motocicleta, modelo Triax, de placa de rodaje 1764-GP. Luego de una tenaz persecución capturó al conductor C. A. T. D. (20), el mismo que portaba un cartucho de dinamita. El pasajero de la moto huyó a pie realizando disparos contra la policía, bajo fuego cruzado se refugió en una vivienda donde finalmente fue detenido siendo identificado con las iniciales L. J. Ch. N. (25). Los custodios le hallaron un arma de fuego.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://andina.pe/agencia/noticia-llegaron-a-piura-los-dos-primeros-puentes-modulares-para-atender-emergencias-por-nino-1091160.aspx</t>
+          <t>https://eltiempo.pe/local/dos-gatilleros-matan-a-sujeto-y-hieren-a-otro-en-paita-pero-policia-los-captura/</t>
         </is>
       </c>
     </row>
@@ -788,17 +827,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Advierten incremento de casos de cáncer infantil en Piura</t>
+          <t>Advierten que la sensación del calor podría llegar a los 39°C en la región Piura</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>El cáncer infantil en Piura registra un incremento progresivo en los últimos años, situación que ha generado preocupación entre las autoridades sanitarias de la región. Jean Martín Galecio, médico oncólogo y coordinador de la estrategia del cáncer de la Dirección Regional de Salud (Diresa) Piura, pidió a los padres de familia prestar atención a los signos y síntomas que puedan presentar sus hijos. El especialista señaló que reconocer las señales de alerta y buscar atención médica de manera oportuna puede marcar una diferencia importante en el tratamiento de niños y adolescentes. Según explicó, en muchos casos las primeras manifestaciones pueden confundirse con enfermedades comunes. “En estos últimos años viene incrementándose progresivamente”, señaló Galecio, quien destacó la importancia de identificar la enfermedad a tiempo debido a que un tratamiento oportuno puede permitir la curación de los menores. ¿Cuántos casos de cáncer infantil se reportaron en Piura? De acuerdo con la información proporcionada por el especialista de la Diresa, durante el 2025 se reportaron 200 casos de cáncer infantil en Piura . La cifra forma parte del panorama que preocupa a las autoridades sanitarias y refuerza el llamado a mejorar la detección temprana. La Diresa Piura también viene trabajando en el fortalecimiento del registro de casos de cáncer en la región. En mayo de 2026, la institución informó que inició una asistencia técnica junto con el Instituto Nacional de Enfermedades Neoplásicas (INEN) para mejorar el Registro de Cáncer de Base Poblacional y contar con información más precisa y actualizada. Según la Diresa Piura , este trabajo permitirá fortalecer la vigilancia epidemiológica y la atención de los pacientes. ¿Qué tipos de cáncer afectan con mayor frecuencia a los niños? Entre las enfermedades oncológicas más frecuentes en la población infantil se encuentra la leucemia , además de los tumores cerebrales y los linfomas. También pueden presentarse tumores renales y óseos, entre otros tipos de neoplasias. El Ministerio de Salud (Minsa) señala que la leucemia es el tipo de cáncer más frecuente entre niñas, niños y adolescentes en el Perú. La institución explica que el cáncer infantil comprende un conjunto de enfermedades que pueden presentarse antes de los 19 años y que, a diferencia de muchos tipos de cáncer en adultos, no puede prevenirse mediante acciones específicas, por lo que la detección temprana adquiere especial importancia. Para el Minsa, la identificación oportuna de los síntomas permite que los profesionales de salud realicen una evaluación, determinen si existe sospecha de una enfermedad oncológica y, de ser necesario, deriven al menor a un establecimiento especializado. De acuerdo con información oficial del Minsa , el diagnóstico temprano y el tratamiento adecuado aumentan las posibilidades de curación. Cáncer infantil en Piura: ¿cuáles son los principales signos de alerta? El médico Jean Martín Galecio mencionó varios síntomas que deben llamar la atención de los padres. Entre ellos se encuentran el dolor persistente de huesos y la fiebre que no desaparece , además de la aparición de moretones en la piel sin una causa evidente. También pueden presentarse sangrados espontáneos por la nariz o las encías, así como tumoraciones o aumentos de volumen en distintas partes del cuerpo. Los ganglios aumentados en zonas como el cuello o las axilas y el incremento del volumen del abdomen son otras señales que requieren una evaluación médica. El Minsa incluye entre sus principales señales de alerta la fiebre durante más de siete días, ganglios duros de más de dos centímetros en cuello, axilas o ingle, palidez progresiva, moretones espontáneos, sangrado reciente de nariz o encías y dolor persistente en los huesos. Según el Ministerio de Salud , ante uno o más de estos signos se debe acudir a un establecimiento de salud para una evaluación. Fiebre, moretones y dolor de huesos Una fiebre que permanece durante varios días, especialmente cuando no existe una causa clara, merece atención. Lo mismo ocurre con el dolor de huesos que persiste y llega a limitar las actividades habituales del menor. Los moretones o pequeños puntos rojos que aparecen de manera espontánea también forman parte de las señales que los especialistas recomiendan vigilar. En algunos casos pueden acompañarse de palidez, cansancio o sangrado. Bultos, ganglios y aumento del abdomen Otra señal que no debe pasar desapercibida es la aparición de una masa o aumento de volumen en alguna parte del cuerpo. Esto puede ocurrir en el cuello, las axilas, la ingle o el abdomen. El Minsa recomienda prestar especial atención a los ganglios duros de más de dos centímetros y a cualquier aumento de volumen que aparezca sin signos claros de inflamación. Estos síntomas no significan necesariamente que un niño tenga cáncer, pero sí justifican una evaluación médica. Dolor de cabeza, vómitos y cambios en la visión Los dolores de cabeza persistentes acompañados de vómitos también figuran entre las señales de alerta. De igual manera, una mancha blanca en la pupila o la aparición repentina de estrabismo requieren una valoración médica. La información oficial del Minsa advierte que algunos de estos síntomas pueden parecerse a los de enfermedades frecuentes de la infancia. Por ello, la recomendación no es asumir que se trata de una neoplasia, sino consultar con un profesional de salud cuando las manifestaciones sean persistentes o llamen especialmente la atención. ¿Por qué es importante detectar temprano el cáncer infantil? La detección temprana es uno de los principales factores relacionados con las posibilidades de recuperación de los menores. El Minsa sostiene que el diagnóstico oportuno permite iniciar el tratamiento en una etapa en la que existen mayores posibilidades de respuesta. En el caso de la leucemia infantil, por ejemplo, los síntomas pueden aparecer de manera relativamente rápida. Cansancio, palidez, fiebre, pérdida de peso, moretones o sangrados pueden ser algunas de sus manifestaciones. Para el Minsa , la identificación de estas señales y la consulta médica temprana son fundamentales para iniciar el diagnóstico correspondiente. ¿Qué deben hacer los padres ante una señal de alerta? Ante la presencia persistente de alguno de estos síntomas, los padres o cuidadores deben llevar al menor a un establecimiento de salud para que sea evaluado por profesionales. Un síntoma aislado no significa necesariamente que exista cáncer, pero tampoco debe ser ignorado cuando persiste, empeora o afecta las actividades habituales del niño. El Ministerio de Salud dispone además de la Línea 113 Salud para orientación gratuita. Los usuarios pueden llamar desde cualquier operador y seleccionar la opción 3 para recibir información relacionada con salud. El Minsa también publica una guía oficial sobre los signos y síntomas de alerta del cáncer infantil . En Piura, el llamado de la Diresa apunta precisamente a evitar que las señales sean ignoradas y a que los menores puedan acceder a una evaluación médica cuando aparezcan síntomas que se mantienen en el tiempo.</t>
+          <t>El Senamhi Piura informó que durante el mes, se registraron temperaturas de hasta 37,2°C en Chulucanas, Piura. No descartan que la sensación de calor pueda alcanzar los 39 °C en Piura. Así lo señaló el especialista del Senamhi Piura, Héctor Yauri quien indicó que este panorama se podría dar por diversos factores, con lo cual la población deberá tomar sus precauciones. El Senamhi informó que durante las últimas semanas las temperaturas se han mantenido por encima de sus valores normales, especialmente las temperaturas máximas. MAGNITUD FUERTE Explican que esta situación estaría “asociada principalmente a la persistencia de anomalías positivas de la temperatura superficial del mar frente a la costa de Piura y en la región Niño 1+2”. “Se espera que las temperaturas del aire continúen registrando valores relativamente elevados durante las próximas semanas, debido a la persistencia de temperaturas superficiales del mar por encima de lo normal en la región Niño 1+2. Estas condiciones son consistentes con la evolución del evento Niño Costero, que actualmente presenta magnitud fuerte, favoreciendo la persistencia de temperaturas superiores a los valores climatológicos para la temporada”, indicó el especialista Fabricio Fabián Herrera. Asimismo, de acuerdo al aviso meteorológico 161 del Senamhi, no se descarta lluvias dispersas en la costa norte y la presencia de lluvias localizadas en la sierra norte.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/advierten-incremento-de-casos-de-cancer-infantil-en-piura/</t>
+          <t>https://eltiempo.pe/local/advierten-que-la-sensacion-del-calor-podria-llegar-a-los-39c-en-la-region-piura/</t>
         </is>
       </c>
     </row>
@@ -813,17 +852,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UPAO Piura lleva el cine universitario a una nueva edición del Festival Ojo Errante</t>
+          <t>Bajo Piura se levanta y exige obras para evitar inundación</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>La tercera edición del certamen convoca a jóvenes realizadores de todo el país, quienes presentarán sus cortometrajes de ficción, documental y animación hasta el 9 de octubre. El talento audiovisual universitario tiene un nuevo espacio de encuentro en Piura. El Programa de Estudio de Comunicación y Medios Digitales de la Universidad Privada Antenor Orrego (UPAO) filial Piura desarrollará la tercera edición del Festival de Cortometrajes Universitarios Ojo Errante, una iniciativa que promueve la producción audiovisual de jóvenes universitarios y su difusión desde las regiones. El certamen se desarrollará de manera presencial y tendrá ingreso gratuito. La convocatoria está dirigida a los estudiantes universitarios de comunicación y facultades afines de todo el país, quienes podrán postular cortometrajes realizados en el ámbito académico, entre agosto del 2024 y octubre del 2026. Ficción, documental y animación Los participantes podrán competir en tres categorías oficiales. En ficción, se recibirán obras basadas en personajes, situaciones y conflictos narrativos imaginarios, con una duración de 5 a 20 minutos. En documental, podrán participar obras de no ficción construidas a partir de hechos, realidades o espacios interpretados por el realizador, con una duración de 5 a 20 minutos. Por su parte, la categoría animación comprende creaciones realizadas mediante técnicas tradicionales, digitales o mixtas, con una duración de 30 segundos a 20 minutos. Inscripciones hasta el 9 de octubre Para la filial Piura, la convocatoria estará abierta hasta el 9 de octubre del 2026, hasta las 11:59 p. m. La exhibición oficial de los trabajos se realizará el 29 de octubre del presente. La inscripción es gratuita y se realizará exclusivamente de manera virtual. Los participantes deberán presentar el cortometraje en formato MP4 H.264 Full HD o 4K, además del póster, teaser y la evidencia del curso universitario y docente responsable. Un espacio para reconocer el talento emergente Los trabajos serán evaluados por un comité especializado, que considerará criterios como la originalidad, la coherencia narrativa y la resolución técnica. El festival otorgará un reconocimiento al mejor cortometraje y menciones honrosas al segundo mejor trabajo de cada categoría. Además, los equipos seleccionados recibirán constancias de participación. Acerca del Festival Ojo Errante El Festival de Cortometrajes Universitarios Ojo Errante es una plataforma cultural y académica impulsada por el Programa de Estudio de Comunicación y Medios Digitales de la UPAO. De este modo se promueve la visibilidad, circulación y experimentación de la producción audiovisual realizada por jóvenes universitarios. A través de proyecciones presenciales, circuitos itinerantes y espacios formativos en Piura, el festival fomenta el desarrollo de la industria cinematográfica emergente desde las regiones. Para más detalles o información, los interesados pueden comunicarse través del siguiente correo: [email protected]</t>
+          <t>La población no quiere ser expectante de como apenas siete maquinarias pesadas trabajan en la descolmatación del río Piura, desde el puente Grau hasta el puente Independencia, sin haberse considerado obras adicionales como el reforzamiento de las defensas ribereñas, los diques de contención, entre otras obras que permitan mitigar el impacto del Fenómeno El Niño (FEN) que se avecina. Por ello ayer, y tras una asamblea, dirigentes de los distritos de Catacaos, Cura Mori y El Tallán acordaron realizar una marcha de protesta el 14 de setiembre a partir de las 8:00 a.m. bajo el lema “Inundación nunca más”. La población está dispuesta a bloquear las vías hasta ser escuchados por las autoridades. «Es una burla» Víctor Chunga, presidente del Frente de reconstrucción de pueblos afectados por el Niño Costero 2017, calificó como una “burla” que en su primera visita a Piura la presidenta Keiko Fujimori anunciara una inversión de 140 millones y un pull de maquinaria para los trabajos de descolmatación y no se está cumpliendo. “Anunció 140 millones, luego 129 millones, pero no está desglosado cuánto le toca a Piura y los trabajos no van ni al 30%. Ahora en la descolmatación (hacia el Bajo Piura) solo están retirando 90 centímetros de sedimento, eso es limpieza no descolmatación”, indicó. Para octubre prometen terminar descolmatación Tras la denuncia del diputado Félix Chang Apuy, sobre la paralización de los trabajos de descolmatación del río Piura, el supervisor de estos trabajos, Ítalo Cuba, señaló que ya solucionaron el tema administrativo de los contratos del personal y se ha retomado los trabajos en el tramo entre la represa Los Ejidos y el puente Bolognesi. Informó que 20 maquinarias pesadas del Gobierno Regional se sumarán a los trabajos, con lo cual esperan culminar los mismos antes de las lluvias pronosticadas para noviembre. “A mediados de octubre se quiere terminar todo esto”, indicó el supervisor quien agregó que buscan recuperar un encausamiento del río con capacidad para 3000 m3/s.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/upao-piura-lleva-el-cine-universitario-a-una-nueva-edicion-del-festival-ojo-errante/</t>
+          <t>https://eltiempo.pe/local/bajo-piura-se-levanta-y-exige-obras-para-evitar-inundacion/</t>
         </is>
       </c>
     </row>
@@ -838,17 +877,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>¿Quiénes estuvieron detrás de asesinatos en Sullana?</t>
+          <t>UPAO Piura lleva el cine universitario a una nueva edición del Festival Ojo Errante</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>La violencia criminal continúa golpeando a la provincia de Sullana. Con los últimos hechos de sangre, ya son 46 las personas asesinadas por sicarios en lo que va del año, mientras que sólo en los primeros días de septiembre se han registrado cuatro homicidios, situación que mantiene preocupada a la población. Sin embargo, se abre la interrogante sobre el último episodio: ¿quienes estuvieron detrás del execrable baño de sangre? Alcohol, bala y tragedia El último ataque ocurrió en el sector Manuel Seoane, donde dos mujeres fueron asesinadas a balazos y otros dos sujetos quedaron heridos cuando se encontraban en una vivienda departiendo bebidas alcohólicas junto a otras personas. Una de las víctimas mortales fue identificada como Loren Valdiviezo Nole, de 28 años, quien se encontraba en estado de gestación. La joven deja en la orfandad a tres menores de edad. Retorno mortal Sus familiares exigieron a la Policía esclarecer el crimen y determinar quiénes estuvieron detrás del ataque. Aseguraron que Loren no tenía problemas con ninguna persona y que nunca había recibido amenazas. Se dedicaba a la venta de parrilladas y hamburguesas durante fiestas de aniversario y celebraciones patronales. Precisamente, junto a su hermana Greysi se encontraba preparando sus actividades comerciales para el aniversario del distrito de Ignacio Escudero. Según relató Greysi, la noche del crimen Loren ya había salido de la vivienda atacada, pero decidió regresar. Minutos después se escucharon los disparos. Estuvo en el lugar equivocado “Mi hermana estuvo en el lugar equivocado, es lo único que podemos decir, solo queremos que se esclarezca lo ocurrido”, manifestó Greysi Valdiviezo al diario La Hora. La segunda dama asesinada, Sheila Anabelen Viera Elías (30), quien también deja en la orfandad a tres niños, sus familiares, evitaron dar declaraciones y mayores detalles de lo ocurrido. La mañana de ayer su padre esperaba que culminara la necropsia en la morgue legal para retirar el cuerpo y trasladarlo a la calle Cusco, cuadra 8, en Bellavista, donde será velado. La Policía, desde la misma noche del lunes, puso en marcha un operativo que ayer dio resultados con la detención de un gatillero.</t>
+          <t>La tercera edición del certamen convoca a jóvenes realizadores de todo el país, quienes presentarán sus cortometrajes de ficción, documental y animación hasta el 9 de octubre. El talento audiovisual universitario tiene un nuevo espacio de encuentro en Piura. El Programa de Estudio de Comunicación y Medios Digitales de la Universidad Privada Antenor Orrego (UPAO) filial Piura desarrollará la tercera edición del Festival de Cortometrajes Universitarios Ojo Errante, una iniciativa que promueve la producción audiovisual de jóvenes universitarios y su difusión desde las regiones. El certamen se desarrollará de manera presencial y tendrá ingreso gratuito. La convocatoria está dirigida a los estudiantes universitarios de comunicación y facultades afines de todo el país, quienes podrán postular cortometrajes realizados en el ámbito académico, entre agosto del 2024 y octubre del 2026. Ficción, documental y animación Los participantes podrán competir en tres categorías oficiales. En ficción, se recibirán obras basadas en personajes, situaciones y conflictos narrativos imaginarios, con una duración de 5 a 20 minutos. En documental, podrán participar obras de no ficción construidas a partir de hechos, realidades o espacios interpretados por el realizador, con una duración de 5 a 20 minutos. Por su parte, la categoría animación comprende creaciones realizadas mediante técnicas tradicionales, digitales o mixtas, con una duración de 30 segundos a 20 minutos. Inscripciones hasta el 9 de octubre Para la filial Piura, la convocatoria estará abierta hasta el 9 de octubre del 2026, hasta las 11:59 p. m. La exhibición oficial de los trabajos se realizará el 29 de octubre del presente. La inscripción es gratuita y se realizará exclusivamente de manera virtual. Los participantes deberán presentar el cortometraje en formato MP4 H.264 Full HD o 4K, además del póster, teaser y la evidencia del curso universitario y docente responsable. Un espacio para reconocer el talento emergente Los trabajos serán evaluados por un comité especializado, que considerará criterios como la originalidad, la coherencia narrativa y la resolución técnica. El festival otorgará un reconocimiento al mejor cortometraje y menciones honrosas al segundo mejor trabajo de cada categoría. Además, los equipos seleccionados recibirán constancias de participación. Acerca del Festival Ojo Errante El Festival de Cortometrajes Universitarios Ojo Errante es una plataforma cultural y académica impulsada por el Programa de Estudio de Comunicación y Medios Digitales de la UPAO. De este modo se promueve la visibilidad, circulación y experimentación de la producción audiovisual realizada por jóvenes universitarios. A través de proyecciones presenciales, circuitos itinerantes y espacios formativos en Piura, el festival fomenta el desarrollo de la industria cinematográfica emergente desde las regiones. Para más detalles o información, los interesados pueden comunicarse través del siguiente correo: [email protected]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/quienes-estuvieron-detras-de-asesinatos-en-sullana/</t>
+          <t>https://eltiempo.pe/local/upao-piura-lleva-el-cine-universitario-a-una-nueva-edicion-del-festival-ojo-errante/</t>
         </is>
       </c>
     </row>
@@ -863,17 +902,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Piura: en menos de 72 horas, delincuentes asesinan a ocho personas en la región</t>
+          <t>¿Quiénes estuvieron detrás de asesinatos en Sullana?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>La violencia criminal golpeó nuevamente a la región Piura . En menos de 72 horas, ocho personas fueron asesinadas en distintos hechos registrados en Sullana, Castilla, Paita y Talara. Entre las víctimas se encuentra un menor de 13 años y tres personas que murieron durante un ataque armado ocurrido en el asentamiento humano Manuel Seoane, en Sullana. Los homicidios se registraron entre la noche del domingo 6 y el lunes 7 de setiembre, en una seguidilla de hechos violentos que también dejó personas heridas y motivó operativos policiales en diferentes puntos de la región. Los casos presentan características similares, como el uso de armas de fuego y, en algunos ataques, la participación de sujetos que se movilizaban en motocicletas. Sin embargo, hasta el momento no existe información oficial que permita establecer que todos los crímenes estén relacionados. ¿Quiénes son las ocho víctimas asesinadas en Piura? El balance de los hechos registrados en este periodo incluye a Alexis Arellano Gómez , asesinado en el sector Salaverry de Sullana; Fernando Castillo , víctima de un ataque en Castilla; y Giancarlo Jiménez Hernández , asesinado en Paita Alta. A ellos se suma un adolescente de 13 años , asesinado la noche del domingo en Sullana. También figuran las tres víctimas mortales del ataque ocurrido la noche del lunes en Manuel Seoane: Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . El octavo caso corresponde a un hombre conocido como “Van Dan” , quien había trabajado como sereno y fue asesinado en el distrito de La Brea-Negritos, en la provincia de Talara. Sullana: asesinan a menor de 13 años en un mototaxi Uno de los casos que más conmoción provocó ocurrió la noche del domingo en Sullana. Un adolescente de 13 años fue asesinado cuando viajaba como pasajero en un mototaxi por la intersección de la calle Túpac Amaru con la avenida Par Vial, en el asentamiento humano 17 de Enero. El ataque ocurrió aproximadamente a las 10:40 de la noche. Según las primeras diligencias, el vehículo habría quedado detenido debido a un desperfecto mecánico. En ese momento, sujetos que se desplazaban en una motocicleta llegaron hasta el mototaxi y dispararon contra el menor. Uno de los proyectiles impactó en su cabeza y le provocó la muerte en el lugar. Sus acompañantes huyeron de la zona, mientras la víctima quedó junto al vehículo. Un tatuaje permitió identificar al adolescente La identificación del menor se realizó posteriormente en la morgue legal. Una familiar acudió ante las autoridades y logró reconocerlo por un tatuaje que llevaba en el brazo derecho con el nombre “Alexander”. La Policía continúa con las diligencias para establecer las circunstancias exactas del crimen. Entre las hipótesis preliminares figura un posible ajuste de cuentas, aunque esta versión todavía debe ser corroborada por los investigadores. Alexis Arellano Gómez fue asesinado en Sullana Otro de los homicidios registrados durante este periodo ocurrió en el sector Salaverry, en Sullana. La víctima fue identificada como Alexis Arellano Gómez . El asesinato forma parte de los hechos violentos registrados durante estas horas en la provincia. La Policía inició las diligencias correspondientes para recoger evidencias, identificar a los responsables y establecer el móvil del ataque. Fernando Castillo fue asesinado en Castilla La ola de violencia también alcanzó Castilla, en la provincia de Piura. Fernando Castillo fue asesinado en circunstancias que son investigadas por las autoridades. El caso se suma a los demás homicidios registrados en la región durante el mismo periodo. Los agentes buscan reconstruir los momentos previos al crimen y determinar quiénes participaron en el ataque. Paita: asesinan a Giancarlo Jiménez Hernández En Paita Alta, Giancarlo Jiménez Hernández, de 33 años , fue asesinado la noche del lunes durante un ataque perpetrado por sujetos que se movilizaban en una motocicleta. El joven caminaba junto a William Daniel Aldana Prado , de 24 años, por la parte posterior de las empresas de transporte Andrea y Santangel cuando fueron interceptados. Según la información preliminar, el pasajero de la motocicleta sacó un arma de fuego y disparó contra ambos. Los heridos fueron trasladados de emergencia al Hospital Nuestra Señora de las Mercedes. Sin embargo, el médico de turno certificó la muerte de Giancarlo Jiménez debido a una hemorragia intracraneal provocada por un proyectil de arma de fuego. William Aldana quedó gravemente herido y permanecía con pronóstico reservado. Dos sospechosos fueron capturados Tras el ataque, agentes de la Comisaría Ciudad del Pescador iniciaron la búsqueda de los responsables. La motocicleta fue ubicada en inmediaciones del colegio Lunitas de Paita y los policías iniciaron una persecución. El conductor, identificado con las iniciales C. A. T. D., de 20 años, fue intervenido. De acuerdo con la información proporcionada, durante el operativo se le encontró un cartucho de dinamita. El pasajero huyó a pie y, según la versión policial, realizó disparos contra los agentes antes de refugiarse en una vivienda. Finalmente fue detenido e identificado con las iniciales L. J. Ch. N., de 25 años. Los agentes le habrían encontrado un arma de fuego. Talara: exsereno es asesinado dentro de un restaurante Otro de los crímenes ocurrió en la provincia de Talara. Un hombre conocido como “Van Dan” , quien había trabajado como sereno y era propietario de un gimnasio en el distrito de La Brea-Negritos, fue asesinado dentro del restaurante La Caleta 10, ubicado en el asentamiento Mario Aguirre. Según la información preliminar, un sujeto irrumpió en el segundo piso del establecimiento y disparó varias veces contra la víctima. El hombre murió pocos segundos después del ataque. La Policía investiga las circunstancias del homicidio y busca establecer si existieron amenazas previas, conflictos personales u otros elementos que permitan determinar el móvil. Sullana: tres personas mueren en ataque armado en Manuel Seoane La noche del lunes 7 de setiembre, un ataque armado registrado en un puesto de venta de comida ubicado en el pasaje Municipal del asentamiento humano Manuel Seoane, en Sullana, dejó tres personas fallecidas y una herida de gravedad . De acuerdo con la información preliminar, varios sujetos armados llegaron hasta el establecimiento y dispararon contra un grupo de personas que se encontraba reunido alrededor de una mesa. Como consecuencia del atentado perdieron la vida Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . Asimismo, Carlos Daniel Cornejo Lupú resultó gravemente herido y fue trasladado a un establecimiento de salud para recibir atención médica. Criminalística recogió evidencias en la escena Tras el ataque, agentes de la División de Investigación Criminal (Divincri) y personal de Criminalística acudieron al lugar para realizar las diligencias correspondientes. Los especialistas recogieron evidencias e indicios balísticos que podrían ayudar a reconstruir el ataque e identificar a los responsables. Las autoridades también iniciaron las investigaciones para determinar el móvil del triple homicidio. Una de las víctimas estaba embarazada Entre las víctimas se encontraba Lady Lore Valdiviezo Nole, de 28 años , quien tenía aproximadamente seis meses de gestación. De acuerdo con la información proporcionada por sus familiares, la joven se dedicaba a la venta de parrilladas y hamburguesas durante fiestas, aniversarios y actividades patronales. Su hermana Greysi relató que ambas venían preparando actividades comerciales relacionadas con el aniversario del distrito de Ignacio Escudero. Según su versión, Loren había salido inicialmente de la vivienda donde ocurrió el ataque, pero decidió regresar. Poco después se escucharon los disparos. La familia pidió a las autoridades esclarecer el crimen y determinar quiénes estuvieron detrás del ataque. ¿Qué investiga la Policía tras los ocho asesinatos? Los ocho homicidios registrados en este periodo ocurrieron en diferentes puntos de Piura. Por ello, las autoridades deberán determinar si existe alguna relación entre los casos o si se trata de hechos independientes. El uso de armas de fuego y la participación de motocicletas en algunos de los ataques son elementos que forman parte de las diligencias. No obstante, establecer una conexión entre los crímenes requiere evidencias que todavía están siendo recopiladas. Piura permanece bajo medidas contra la criminalidad Los nuevos asesinatos se producen mientras diferentes sectores de la región permanecen bajo medidas especiales frente al incremento de la inseguridad. El Gobierno declaró el estado de emergencia en Piura, Castilla, Veintiséis de Octubre y Catacaos mediante el Decreto Supremo N.° 126-2026. Para el exjefe de la Región Policial de Piura, coronel en retiro Máximo Vargas Hugo, este tipo de medidas no ha generado los resultados que reclama la población. El exmando policial consideró necesario fortalecer la labor policial con recursos, logística e inteligencia. “La población quiere seguridad y están repitiendo lo mismo que han hecho gestiones anteriores”, señaló Vargas Hugo al referirse a las declaratorias de emergencia aplicadas en la región. Sobre el cambio en el comando de la Policía, sostuvo que una modificación en el alto mando no garantiza por sí sola mejores resultados y remarcó la necesidad de proporcionar herramientas adecuadas a los agentes para enfrentar a las organizaciones criminales. Por su parte, el general Daniel Jares, jefe de la Región Policial Piura, informó que durante los primeros días de setiembre se habían contabilizado 12 personas asesinadas . Esta cifra corresponde a un periodo más amplio y no debe confundirse con los ocho homicidios registrados en menos de 72 horas detallados en este reporte.</t>
+          <t>La violencia criminal continúa golpeando a la provincia de Sullana. Con los últimos hechos de sangre, ya son 46 las personas asesinadas por sicarios en lo que va del año, mientras que sólo en los primeros días de septiembre se han registrado cuatro homicidios, situación que mantiene preocupada a la población. Sin embargo, se abre la interrogante sobre el último episodio: ¿quienes estuvieron detrás del execrable baño de sangre? Alcohol, bala y tragedia El último ataque ocurrió en el sector Manuel Seoane, donde dos mujeres fueron asesinadas a balazos y otros dos sujetos quedaron heridos cuando se encontraban en una vivienda departiendo bebidas alcohólicas junto a otras personas. Una de las víctimas mortales fue identificada como Loren Valdiviezo Nole, de 28 años, quien se encontraba en estado de gestación. La joven deja en la orfandad a tres menores de edad. Retorno mortal Sus familiares exigieron a la Policía esclarecer el crimen y determinar quiénes estuvieron detrás del ataque. Aseguraron que Loren no tenía problemas con ninguna persona y que nunca había recibido amenazas. Se dedicaba a la venta de parrilladas y hamburguesas durante fiestas de aniversario y celebraciones patronales. Precisamente, junto a su hermana Greysi se encontraba preparando sus actividades comerciales para el aniversario del distrito de Ignacio Escudero. Según relató Greysi, la noche del crimen Loren ya había salido de la vivienda atacada, pero decidió regresar. Minutos después se escucharon los disparos. Estuvo en el lugar equivocado “Mi hermana estuvo en el lugar equivocado, es lo único que podemos decir, solo queremos que se esclarezca lo ocurrido”, manifestó Greysi Valdiviezo al diario La Hora. La segunda dama asesinada, Sheila Anabelen Viera Elías (30), quien también deja en la orfandad a tres niños, sus familiares, evitaron dar declaraciones y mayores detalles de lo ocurrido. La mañana de ayer su padre esperaba que culminara la necropsia en la morgue legal para retirar el cuerpo y trasladarlo a la calle Cusco, cuadra 8, en Bellavista, donde será velado. La Policía, desde la misma noche del lunes, puso en marcha un operativo que ayer dio resultados con la detención de un gatillero.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-en-menos-de-72-horas-delincuentes-asesinan-a-ocho-personas-en-la-region/</t>
+          <t>https://eltiempo.pe/local/quienes-estuvieron-detras-de-asesinatos-en-sullana/</t>
         </is>
       </c>
     </row>
@@ -888,17 +927,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ODPE Piura recibe material para capacitar a actores electorales</t>
+          <t>Piura: en menos de 72 horas, delincuentes asesinan a ocho personas en la región</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>En el marco de las Elecciones Regionales y Municipales (ERM) 2026, la Oficina Descentralizada de Procesos Electorales (ODPE) Piura recibió el material de capacitación que será empleado en la preparación de los diversos actores electorales que participarán en los comicios del próximo 4 de octubre. Puedes Leer | Bajo Piura se levanta y exige obras para evitar inundación El cargamento, remitido desde el almacén central de la Gerencia de Gestión Electoral de la ONPE en Lurín, arribó a la sede de la ODPE Piura bajo protocolos de seguridad y resguardo para su inmediata verificación, almacenamiento y posterior distribución en los distritos y centros poblados bajo su jurisdicción. Entre los instrumentos recibidos se encuentran materiales pedagógicos que replican con exactitud las condiciones de una mesa de sufragio, los cuales serán utilizados en los talleres que se desarrollarán en las oficinas distritales de la circunscripción electoral, así como en las jornadas masivas de capacitación a miembros de mesa programadas para los días 20 y 27 de setiembre. Asimismo, arribó insumos didácticos dirigidos a los talleres de formación de capacitadores electorales, coordinadores distritales, coordinadores de local de votación y personal de campo que desplegará acciones informativas en los distritos. Mira También | Advierten incremento de casos de cáncer infantil en Piura El jefe de la ODPE Piura, Juan Roel Godofredo Valdivia, señaló que la preparación de los actores electorales constituye una etapa fundamental para garantizar el adecuado desarrollo de los comicios y destacó la importancia de que quienes participarán en la jornada conozcan oportunamente las tareas y responsabilidades que deberán cumplir. Para estos comicios, el organismo electoral instalará en los distritos Piura y Veintiséis de Octubre un total de 884 mesas de sufragio en 67 locales de votación, donde están llamados a sufragar aproximadamente 264 809 electores hábiles. Más información https://erm2026.onpe.gob.pe</t>
+          <t>La violencia criminal golpeó nuevamente a la región Piura . En menos de 72 horas, ocho personas fueron asesinadas en distintos hechos registrados en Sullana, Castilla, Paita y Talara. Entre las víctimas se encuentra un menor de 13 años y tres personas que murieron durante un ataque armado ocurrido en el asentamiento humano Manuel Seoane, en Sullana. Los homicidios se registraron entre la noche del domingo 6 y el lunes 7 de setiembre, en una seguidilla de hechos violentos que también dejó personas heridas y motivó operativos policiales en diferentes puntos de la región. Los casos presentan características similares, como el uso de armas de fuego y, en algunos ataques, la participación de sujetos que se movilizaban en motocicletas. Sin embargo, hasta el momento no existe información oficial que permita establecer que todos los crímenes estén relacionados. ¿Quiénes son las ocho víctimas asesinadas en Piura? El balance de los hechos registrados en este periodo incluye a Alexis Arellano Gómez , asesinado en el sector Salaverry de Sullana; Fernando Castillo , víctima de un ataque en Castilla; y Giancarlo Jiménez Hernández , asesinado en Paita Alta. A ellos se suma un adolescente de 13 años , asesinado la noche del domingo en Sullana. También figuran las tres víctimas mortales del ataque ocurrido la noche del lunes en Manuel Seoane: Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . El octavo caso corresponde a un hombre conocido como “Van Dan” , quien había trabajado como sereno y fue asesinado en el distrito de La Brea-Negritos, en la provincia de Talara. Sullana: asesinan a menor de 13 años en un mototaxi Uno de los casos que más conmoción provocó ocurrió la noche del domingo en Sullana. Un adolescente de 13 años fue asesinado cuando viajaba como pasajero en un mototaxi por la intersección de la calle Túpac Amaru con la avenida Par Vial, en el asentamiento humano 17 de Enero. El ataque ocurrió aproximadamente a las 10:40 de la noche. Según las primeras diligencias, el vehículo habría quedado detenido debido a un desperfecto mecánico. En ese momento, sujetos que se desplazaban en una motocicleta llegaron hasta el mototaxi y dispararon contra el menor. Uno de los proyectiles impactó en su cabeza y le provocó la muerte en el lugar. Sus acompañantes huyeron de la zona, mientras la víctima quedó junto al vehículo. Un tatuaje permitió identificar al adolescente La identificación del menor se realizó posteriormente en la morgue legal. Una familiar acudió ante las autoridades y logró reconocerlo por un tatuaje que llevaba en el brazo derecho con el nombre “Alexander”. La Policía continúa con las diligencias para establecer las circunstancias exactas del crimen. Entre las hipótesis preliminares figura un posible ajuste de cuentas, aunque esta versión todavía debe ser corroborada por los investigadores. Alexis Arellano Gómez fue asesinado en Sullana Otro de los homicidios registrados durante este periodo ocurrió en el sector Salaverry, en Sullana. La víctima fue identificada como Alexis Arellano Gómez . El asesinato forma parte de los hechos violentos registrados durante estas horas en la provincia. La Policía inició las diligencias correspondientes para recoger evidencias, identificar a los responsables y establecer el móvil del ataque. Fernando Castillo fue asesinado en Castilla La ola de violencia también alcanzó Castilla, en la provincia de Piura. Fernando Castillo fue asesinado en circunstancias que son investigadas por las autoridades. El caso se suma a los demás homicidios registrados en la región durante el mismo periodo. Los agentes buscan reconstruir los momentos previos al crimen y determinar quiénes participaron en el ataque. Paita: asesinan a Giancarlo Jiménez Hernández En Paita Alta, Giancarlo Jiménez Hernández, de 33 años , fue asesinado la noche del lunes durante un ataque perpetrado por sujetos que se movilizaban en una motocicleta. El joven caminaba junto a William Daniel Aldana Prado , de 24 años, por la parte posterior de las empresas de transporte Andrea y Santangel cuando fueron interceptados. Según la información preliminar, el pasajero de la motocicleta sacó un arma de fuego y disparó contra ambos. Los heridos fueron trasladados de emergencia al Hospital Nuestra Señora de las Mercedes. Sin embargo, el médico de turno certificó la muerte de Giancarlo Jiménez debido a una hemorragia intracraneal provocada por un proyectil de arma de fuego. William Aldana quedó gravemente herido y permanecía con pronóstico reservado. Dos sospechosos fueron capturados Tras el ataque, agentes de la Comisaría Ciudad del Pescador iniciaron la búsqueda de los responsables. La motocicleta fue ubicada en inmediaciones del colegio Lunitas de Paita y los policías iniciaron una persecución. El conductor, identificado con las iniciales C. A. T. D., de 20 años, fue intervenido. De acuerdo con la información proporcionada, durante el operativo se le encontró un cartucho de dinamita. El pasajero huyó a pie y, según la versión policial, realizó disparos contra los agentes antes de refugiarse en una vivienda. Finalmente fue detenido e identificado con las iniciales L. J. Ch. N., de 25 años. Los agentes le habrían encontrado un arma de fuego. Talara: exsereno es asesinado dentro de un restaurante Otro de los crímenes ocurrió en la provincia de Talara. Un hombre conocido como “Van Dan” , quien había trabajado como sereno y era propietario de un gimnasio en el distrito de La Brea-Negritos, fue asesinado dentro del restaurante La Caleta 10, ubicado en el asentamiento Mario Aguirre. Según la información preliminar, un sujeto irrumpió en el segundo piso del establecimiento y disparó varias veces contra la víctima. El hombre murió pocos segundos después del ataque. La Policía investiga las circunstancias del homicidio y busca establecer si existieron amenazas previas, conflictos personales u otros elementos que permitan determinar el móvil. Sullana: tres personas mueren en ataque armado en Manuel Seoane La noche del lunes 7 de setiembre, un ataque armado registrado en un puesto de venta de comida ubicado en el pasaje Municipal del asentamiento humano Manuel Seoane, en Sullana, dejó tres personas fallecidas y una herida de gravedad . De acuerdo con la información preliminar, varios sujetos armados llegaron hasta el establecimiento y dispararon contra un grupo de personas que se encontraba reunido alrededor de una mesa. Como consecuencia del atentado perdieron la vida Sheyla Viera Elías, Lady Lore Valdiviezo Nole y Daniel Alfonso Páucar Manchay . Asimismo, Carlos Daniel Cornejo Lupú resultó gravemente herido y fue trasladado a un establecimiento de salud para recibir atención médica. Criminalística recogió evidencias en la escena Tras el ataque, agentes de la División de Investigación Criminal (Divincri) y personal de Criminalística acudieron al lugar para realizar las diligencias correspondientes. Los especialistas recogieron evidencias e indicios balísticos que podrían ayudar a reconstruir el ataque e identificar a los responsables. Las autoridades también iniciaron las investigaciones para determinar el móvil del triple homicidio. Una de las víctimas estaba embarazada Entre las víctimas se encontraba Lady Lore Valdiviezo Nole, de 28 años , quien tenía aproximadamente seis meses de gestación. De acuerdo con la información proporcionada por sus familiares, la joven se dedicaba a la venta de parrilladas y hamburguesas durante fiestas, aniversarios y actividades patronales. Su hermana Greysi relató que ambas venían preparando actividades comerciales relacionadas con el aniversario del distrito de Ignacio Escudero. Según su versión, Loren había salido inicialmente de la vivienda donde ocurrió el ataque, pero decidió regresar. Poco después se escucharon los disparos. La familia pidió a las autoridades esclarecer el crimen y determinar quiénes estuvieron detrás del ataque. ¿Qué investiga la Policía tras los ocho asesinatos? Los ocho homicidios registrados en este periodo ocurrieron en diferentes puntos de Piura. Por ello, las autoridades deberán determinar si existe alguna relación entre los casos o si se trata de hechos independientes. El uso de armas de fuego y la participación de motocicletas en algunos de los ataques son elementos que forman parte de las diligencias. No obstante, establecer una conexión entre los crímenes requiere evidencias que todavía están siendo recopiladas. Piura permanece bajo medidas contra la criminalidad Los nuevos asesinatos se producen mientras diferentes sectores de la región permanecen bajo medidas especiales frente al incremento de la inseguridad. El Gobierno declaró el estado de emergencia en Piura, Castilla, Veintiséis de Octubre y Catacaos mediante el Decreto Supremo N.° 126-2026. Para el exjefe de la Región Policial de Piura, coronel en retiro Máximo Vargas Hugo, este tipo de medidas no ha generado los resultados que reclama la población. El exmando policial consideró necesario fortalecer la labor policial con recursos, logística e inteligencia. “La población quiere seguridad y están repitiendo lo mismo que han hecho gestiones anteriores”, señaló Vargas Hugo al referirse a las declaratorias de emergencia aplicadas en la región. Sobre el cambio en el comando de la Policía, sostuvo que una modificación en el alto mando no garantiza por sí sola mejores resultados y remarcó la necesidad de proporcionar herramientas adecuadas a los agentes para enfrentar a las organizaciones criminales. Por su parte, el general Daniel Jares, jefe de la Región Policial Piura, informó que durante los primeros días de setiembre se habían contabilizado 12 personas asesinadas . Esta cifra corresponde a un periodo más amplio y no debe confundirse con los ocho homicidios registrados en menos de 72 horas detallados en este reporte.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/odpe-piura-recibe-material-para-capacitar-a-actores-electorales/</t>
+          <t>https://eltiempo.pe/local/piura-en-menos-de-72-horas-delincuentes-asesinan-a-ocho-personas-en-la-region/</t>
         </is>
       </c>
     </row>
@@ -913,17 +952,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dos gatilleros matan a sujeto y hieren a otro en Paita, pero Policía los captura</t>
+          <t>Advierten incremento de casos de cáncer infantil en Piura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>A cinco se incrementaron los asesinatos del pasado lunes en la región, luego que gatilleros motorizados asesinaran a tiros a joven en Paita alta y dejarán gravemente herido a su amigo. Esta vez, la Policía Nacional en rápida repuesta capturó a balazos dos sospechosos, incautando una motocicleta y un arma de fuego. Transcurría las 9:50 de la noche del lunes, cuando los amigos Giancarlo Jiménez Hernández, de 33 años, y William Daniel Aldana Prado, de 24 años, caminaban por la parte posterior de las empresas de transporte Andrea y Santangel, fueron interceptados por una motocicleta. Disparó a matar El sujeto que iba como pasajero sacó un arma de fuego y disparó a matar contra los dos amigos. Los ocupantes de la motocicleta al ver caer a sus blancos se dieron a la fuga por las calles de Paita Alta. Los dos amigos gravemenre heridos fueron socorridos y trasladados de emergencia al Hospital Nuestra Señora de las Mercedes.Lamentablemente, el médico de turno, Ricardo Pereira certificó la muerte de Giancarlo Jiménez por hemorragia intercraneal por disparo de arma de fuego. En tanto, dio el diagnóstico oara Willian Aldaba de traumatismo abdominal abierto por proyectil con arma de fuego. Su estado de salud es de pronostico reservado. Persecución y captura Un grupo de agentes de la Comisaría Ciudad del Pescador con las características de la moto y los sujetos a inmediaciones del colegio “Lunitas de Paita” localizó la motocicleta, modelo Triax, de placa de rodaje 1764-GP. Luego de una tenaz persecución capturó al conductor C. A. T. D. (20), el mismo que portaba un cartucho de dinamita. El pasajero de la moto huyó a pie realizando disparos contra la policía, bajo fuego cruzado se refugió en una vivienda donde finalmente fue detenido siendo identificado con las iniciales L. J. Ch. N. (25). Los custodios le hallaron un arma de fuego.</t>
+          <t>El cáncer infantil en Piura registra un incremento progresivo en los últimos años, situación que ha generado preocupación entre las autoridades sanitarias de la región. Jean Martín Galecio, médico oncólogo y coordinador de la estrategia del cáncer de la Dirección Regional de Salud (Diresa) Piura, pidió a los padres de familia prestar atención a los signos y síntomas que puedan presentar sus hijos. El especialista señaló que reconocer las señales de alerta y buscar atención médica de manera oportuna puede marcar una diferencia importante en el tratamiento de niños y adolescentes. Según explicó, en muchos casos las primeras manifestaciones pueden confundirse con enfermedades comunes. “En estos últimos años viene incrementándose progresivamente”, señaló Galecio, quien destacó la importancia de identificar la enfermedad a tiempo debido a que un tratamiento oportuno puede permitir la curación de los menores. ¿Cuántos casos de cáncer infantil se reportaron en Piura? De acuerdo con la información proporcionada por el especialista de la Diresa, durante el 2025 se reportaron 200 casos de cáncer infantil en Piura . La cifra forma parte del panorama que preocupa a las autoridades sanitarias y refuerza el llamado a mejorar la detección temprana. La Diresa Piura también viene trabajando en el fortalecimiento del registro de casos de cáncer en la región. En mayo de 2026, la institución informó que inició una asistencia técnica junto con el Instituto Nacional de Enfermedades Neoplásicas (INEN) para mejorar el Registro de Cáncer de Base Poblacional y contar con información más precisa y actualizada. Según la Diresa Piura , este trabajo permitirá fortalecer la vigilancia epidemiológica y la atención de los pacientes. ¿Qué tipos de cáncer afectan con mayor frecuencia a los niños? Entre las enfermedades oncológicas más frecuentes en la población infantil se encuentra la leucemia , además de los tumores cerebrales y los linfomas. También pueden presentarse tumores renales y óseos, entre otros tipos de neoplasias. El Ministerio de Salud (Minsa) señala que la leucemia es el tipo de cáncer más frecuente entre niñas, niños y adolescentes en el Perú. La institución explica que el cáncer infantil comprende un conjunto de enfermedades que pueden presentarse antes de los 19 años y que, a diferencia de muchos tipos de cáncer en adultos, no puede prevenirse mediante acciones específicas, por lo que la detección temprana adquiere especial importancia. Para el Minsa, la identificación oportuna de los síntomas permite que los profesionales de salud realicen una evaluación, determinen si existe sospecha de una enfermedad oncológica y, de ser necesario, deriven al menor a un establecimiento especializado. De acuerdo con información oficial del Minsa , el diagnóstico temprano y el tratamiento adecuado aumentan las posibilidades de curación. Cáncer infantil en Piura: ¿cuáles son los principales signos de alerta? El médico Jean Martín Galecio mencionó varios síntomas que deben llamar la atención de los padres. Entre ellos se encuentran el dolor persistente de huesos y la fiebre que no desaparece , además de la aparición de moretones en la piel sin una causa evidente. También pueden presentarse sangrados espontáneos por la nariz o las encías, así como tumoraciones o aumentos de volumen en distintas partes del cuerpo. Los ganglios aumentados en zonas como el cuello o las axilas y el incremento del volumen del abdomen son otras señales que requieren una evaluación médica. El Minsa incluye entre sus principales señales de alerta la fiebre durante más de siete días, ganglios duros de más de dos centímetros en cuello, axilas o ingle, palidez progresiva, moretones espontáneos, sangrado reciente de nariz o encías y dolor persistente en los huesos. Según el Ministerio de Salud , ante uno o más de estos signos se debe acudir a un establecimiento de salud para una evaluación. Fiebre, moretones y dolor de huesos Una fiebre que permanece durante varios días, especialmente cuando no existe una causa clara, merece atención. Lo mismo ocurre con el dolor de huesos que persiste y llega a limitar las actividades habituales del menor. Los moretones o pequeños puntos rojos que aparecen de manera espontánea también forman parte de las señales que los especialistas recomiendan vigilar. En algunos casos pueden acompañarse de palidez, cansancio o sangrado. Bultos, ganglios y aumento del abdomen Otra señal que no debe pasar desapercibida es la aparición de una masa o aumento de volumen en alguna parte del cuerpo. Esto puede ocurrir en el cuello, las axilas, la ingle o el abdomen. El Minsa recomienda prestar especial atención a los ganglios duros de más de dos centímetros y a cualquier aumento de volumen que aparezca sin signos claros de inflamación. Estos síntomas no significan necesariamente que un niño tenga cáncer, pero sí justifican una evaluación médica. Dolor de cabeza, vómitos y cambios en la visión Los dolores de cabeza persistentes acompañados de vómitos también figuran entre las señales de alerta. De igual manera, una mancha blanca en la pupila o la aparición repentina de estrabismo requieren una valoración médica. La información oficial del Minsa advierte que algunos de estos síntomas pueden parecerse a los de enfermedades frecuentes de la infancia. Por ello, la recomendación no es asumir que se trata de una neoplasia, sino consultar con un profesional de salud cuando las manifestaciones sean persistentes o llamen especialmente la atención. ¿Por qué es importante detectar temprano el cáncer infantil? La detección temprana es uno de los principales factores relacionados con las posibilidades de recuperación de los menores. El Minsa sostiene que el diagnóstico oportuno permite iniciar el tratamiento en una etapa en la que existen mayores posibilidades de respuesta. En el caso de la leucemia infantil, por ejemplo, los síntomas pueden aparecer de manera relativamente rápida. Cansancio, palidez, fiebre, pérdida de peso, moretones o sangrados pueden ser algunas de sus manifestaciones. Para el Minsa , la identificación de estas señales y la consulta médica temprana son fundamentales para iniciar el diagnóstico correspondiente. ¿Qué deben hacer los padres ante una señal de alerta? Ante la presencia persistente de alguno de estos síntomas, los padres o cuidadores deben llevar al menor a un establecimiento de salud para que sea evaluado por profesionales. Un síntoma aislado no significa necesariamente que exista cáncer, pero tampoco debe ser ignorado cuando persiste, empeora o afecta las actividades habituales del niño. El Ministerio de Salud dispone además de la Línea 113 Salud para orientación gratuita. Los usuarios pueden llamar desde cualquier operador y seleccionar la opción 3 para recibir información relacionada con salud. El Minsa también publica una guía oficial sobre los signos y síntomas de alerta del cáncer infantil . En Piura, el llamado de la Diresa apunta precisamente a evitar que las señales sean ignoradas y a que los menores puedan acceder a una evaluación médica cuando aparezcan síntomas que se mantienen en el tiempo.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/dos-gatilleros-matan-a-sujeto-y-hieren-a-otro-en-paita-pero-policia-los-captura/</t>
+          <t>https://eltiempo.pe/local/advierten-incremento-de-casos-de-cancer-infantil-en-piura/</t>
         </is>
       </c>
     </row>
@@ -934,21 +973,21 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura</t>
+          <t>ODPE Piura recibe material para capacitar a actores electorales</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>El fenómeno “El Niño” (FEN) sigue acumulando energía en el mar frente a las costas de la región y los impactos de este calentamiento son hasta el momento insospechados, según informó el especialista en meteorología del Senamhi Piura, Héctor Yauli. PUEDES LEER ► Es hora de rescatar la cultura de Piura De lo que sí se tiene mayor certeza es que los indicadores de este fenómeno en desarrollo ya superaron los valores previos al Mega Niño que castigó la región entre los años 1997 y 1998. “Lo que ha dicho el Organismo Mundial de Meteorología es que los impactos que pueda generar este Niño en el contexto en el cual se presenta, porque el nivel de calentamiento es muy exacerbado y no se tiene comparación con los años 1997 y 1998. Es una gran cantidad de energía y calor no solamente en la zona tropical donde se desarrolla El Niño sino en todos los océanos el nivel de calentamiento es muy mayor. Se esperan impactos insospechados por la alta incertidumbre que hay. [...] Lo que sí tenemos mucha seguridad es en cuanto a que se van a presentar lluvias bastante fuertes e intensas en los meses de verano”, manifestó. Sobre la magnitud, Yauri indicó que existe una incertidumbre sobre los niveles que se alcanzarán las precipitaciones. Cabe indicar que durante el Mega Niño de 1998, se registró la máxima precipitación el 24 de enero con un valor de 173.6 milímetros de acumulado en una sola lluvia. Esto implica que ese día cayeron más de 173 litros de agua sobre un metro cuadrado. Peores En este punto, Yauli informó que el escenario es mucho más complicado porque no solo es un calentamiento del mar frente a la costa norte, sino en diferentes partes del mundo. “Es un nivel de calentamiento exacerbado que no tiene comparación. Si nos situamos en septiembre de 1997, solamente veíamos el calentamiento de El Niño, pero el océano Pacífico en el norte estaba en condiciones normales, en Chile estaba normal y en el Atlántico igual. Sin embargo, ahora está caliente el norte y sur del Pacífico, e incluso en el Atlántico también está caliente y eso trae otras implicancias y diferente tipo de impactos vinculados a que habrá mucha lluvia en la zona norte del Perú y bastante deficiencia de lluvias en la zona noroeste de Brasil”, destacó Yauli.</t>
+          <t>En el marco de las Elecciones Regionales y Municipales (ERM) 2026, la Oficina Descentralizada de Procesos Electorales (ODPE) Piura recibió el material de capacitación que será empleado en la preparación de los diversos actores electorales que participarán en los comicios del próximo 4 de octubre. Puedes Leer | Bajo Piura se levanta y exige obras para evitar inundación El cargamento, remitido desde el almacén central de la Gerencia de Gestión Electoral de la ONPE en Lurín, arribó a la sede de la ODPE Piura bajo protocolos de seguridad y resguardo para su inmediata verificación, almacenamiento y posterior distribución en los distritos y centros poblados bajo su jurisdicción. Entre los instrumentos recibidos se encuentran materiales pedagógicos que replican con exactitud las condiciones de una mesa de sufragio, los cuales serán utilizados en los talleres que se desarrollarán en las oficinas distritales de la circunscripción electoral, así como en las jornadas masivas de capacitación a miembros de mesa programadas para los días 20 y 27 de setiembre. Asimismo, arribó insumos didácticos dirigidos a los talleres de formación de capacitadores electorales, coordinadores distritales, coordinadores de local de votación y personal de campo que desplegará acciones informativas en los distritos. Mira También | Advierten incremento de casos de cáncer infantil en Piura El jefe de la ODPE Piura, Juan Roel Godofredo Valdivia, señaló que la preparación de los actores electorales constituye una etapa fundamental para garantizar el adecuado desarrollo de los comicios y destacó la importancia de que quienes participarán en la jornada conozcan oportunamente las tareas y responsabilidades que deberán cumplir. Para estos comicios, el organismo electoral instalará en los distritos Piura y Veintiséis de Octubre un total de 884 mesas de sufragio en 67 locales de votación, donde están llamados a sufragar aproximadamente 264 809 electores hábiles. Más información https://erm2026.onpe.gob.pe</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/el-nino-traera-unos-impactos-insospechados-en-la-region-piura/</t>
+          <t>https://eltiempo.pe/local/odpe-piura-recibe-material-para-capacitar-a-actores-electorales/</t>
         </is>
       </c>
     </row>
@@ -963,17 +1002,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dren Maldonado: MTC enviará puente a Piura tras alerta por riesgo de dejar incomunicadas a 60 mil personas</t>
+          <t>El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>La senadora por Piura, Karla Schaefer, informó que el ministro de Transportes y Comunicaciones, Rafael Rey Rey, dispuso el envío de un puente que será utilizado para garantizar la conexión vial ante una eventual afectación del dren Maldonado. Puedes Leer | El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura La situación de riesgo en el dren Maldonado, en el distrito de Veintiséis de Octubre, habría encontrado una respuesta desde el Gobierno central. La senadora por Piura, Karla Schaefer , informó que el Ministerio de Transportes y Comunicaciones (MTC) dispuso el envío de un puente para atender una eventual interrupción de la vía en este sector. Según explicó Schaefer, el pedido fue trasladado al MTC debido a la preocupación por la seguridad de la red vial y el riesgo de que una eventual afectación del dren Maldonado pueda comprometer la comunicación de importantes sectores de Piura. “ El ministro de Transportes y Comunicaciones, Rafael Rey, afirmó que él va a poner el puente ”, señaló la senadora. Schaefer explicó que inicialmente se realizaron consultas tanto al MTC como al Ministerio de Defensa (Mindef), a través de la empresa estatal SIMA Perú , para evaluar una alternativa que permita responder ante una emergencia. Sin embargo, de acuerdo con la parlamentaria, el ministro Rey tomó la decisión de disponer directamente la estructura tras conocer la situación. “Se había hecho la consulta al Ministerio de Transportes y Comunicaciones y al Ministerio de Defensa a través de SIMA Perú. Pero el ministro Rafael Rey, gracias a la delegación de facultades, ni bien vio el tema, dijo: ‘ Yo voy a dar ese puente ’”, declaró. Puente será trasladado a Piura La senadora informó además que la estructura ya habría salido de Lima con destino a Piura y será almacenada temporalmente en Piura Futura , desde donde podrá ser trasladada hacia los puntos que requieran atención. “Hoy han salido de Lima y serán almacenados en Piura Futura para que desde ahí se vayan a varios puntos”, indicó Schaefer. La medida busca contar con una alternativa de conexión ante una eventual emergencia relacionada con el dren Maldonado, especialmente considerando el riesgo advertido para la población de Veintiséis de Octubre. En declaraciones difundidas previamente por El Tiempo , Schaefer había advertido que una eventual afectación del dren podría dejar incomunicadas a unas 60 mil personas y había cuestionado las dificultades generadas por la distribución de competencias entre distintas instituciones del Estado. Schaefer agradece respuesta del MTC La senadora destacó la rapidez con la que, según su versión, el ministro de Transportes habría atendido el pedido. “ Agradecerle al ministro esa eficiencia en solucionar ese problema en que se prioriza la vida ”, manifestó. Asimismo, reconoció el trabajo del director de Puentes, Julio Palacios , y de la Municipalidad Distrital de Veintiséis de Octubre , instituciones que, según indicó, tendrán participación en la gestión relacionada con la estructura. Mira También | ¡Ni los niños se salvan del hampa! Delincuentes saquean colegio y se llevan hasta los juguetes en el Bajo Piura El dren Maldonado es uno de los puntos críticos del sistema de drenaje de Veintiséis de Octubre. En febrero de 2026, el INDECI ya había identificado la necesidad de gestionar requerimientos para garantizar su operatividad, debido a su importancia para la evacuación de aguas pluviales durante lluvias intensas. La atención al dren Maldonado forma parte de una problemática mayor de infraestructura y prevención frente a lluvias en Piura, donde distintas autoridades han advertido sobre la necesidad de acelerar las intervenciones antes de que se presenten emergencias.</t>
+          <t>El fenómeno “El Niño” (FEN) sigue acumulando energía en el mar frente a las costas de la región y los impactos de este calentamiento son hasta el momento insospechados, según informó el especialista en meteorología del Senamhi Piura, Héctor Yauli. PUEDES LEER ► Es hora de rescatar la cultura de Piura De lo que sí se tiene mayor certeza es que los indicadores de este fenómeno en desarrollo ya superaron los valores previos al Mega Niño que castigó la región entre los años 1997 y 1998. “Lo que ha dicho el Organismo Mundial de Meteorología es que los impactos que pueda generar este Niño en el contexto en el cual se presenta, porque el nivel de calentamiento es muy exacerbado y no se tiene comparación con los años 1997 y 1998. Es una gran cantidad de energía y calor no solamente en la zona tropical donde se desarrolla El Niño sino en todos los océanos el nivel de calentamiento es muy mayor. Se esperan impactos insospechados por la alta incertidumbre que hay. [...] Lo que sí tenemos mucha seguridad es en cuanto a que se van a presentar lluvias bastante fuertes e intensas en los meses de verano”, manifestó. Sobre la magnitud, Yauri indicó que existe una incertidumbre sobre los niveles que se alcanzarán las precipitaciones. Cabe indicar que durante el Mega Niño de 1998, se registró la máxima precipitación el 24 de enero con un valor de 173.6 milímetros de acumulado en una sola lluvia. Esto implica que ese día cayeron más de 173 litros de agua sobre un metro cuadrado. Peores En este punto, Yauli informó que el escenario es mucho más complicado porque no solo es un calentamiento del mar frente a la costa norte, sino en diferentes partes del mundo. “Es un nivel de calentamiento exacerbado que no tiene comparación. Si nos situamos en septiembre de 1997, solamente veíamos el calentamiento de El Niño, pero el océano Pacífico en el norte estaba en condiciones normales, en Chile estaba normal y en el Atlántico igual. Sin embargo, ahora está caliente el norte y sur del Pacífico, e incluso en el Atlántico también está caliente y eso trae otras implicancias y diferente tipo de impactos vinculados a que habrá mucha lluvia en la zona norte del Perú y bastante deficiencia de lluvias en la zona noroeste de Brasil”, destacó Yauli.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/dren-maldonado-mtc-enviara-puente-a-piura-tras-alerta-por-riesgo-de-dejar-incomunicadas-a-60-mil-personas/</t>
+          <t>https://eltiempo.pe/local/el-nino-traera-unos-impactos-insospechados-en-la-region-piura/</t>
         </is>
       </c>
     </row>
@@ -988,17 +1027,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Refuerzan la vigilancia de flamencos en humedales de Sechura</t>
+          <t>Los SARE siguen sin mantenimiento para funcionar durante las lluvias</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Unos 4.800 flamencos chilenos ( Phoenicopterus chilensis ) habrían completado este año su etapa de reproducción y desplazamiento en el Estuario de Virrilá y la laguna La Niña , dos importantes humedales ubicados en la provincia de Sechura , en Piura. El registro fue recogido por el Servicio Nacional Forestal y de Fauna Silvestre (Serfor) , organismo adscrito al Ministerio de Desarrollo Agrario y Riego (Midagri), durante las labores de monitoreo de esta especie migratoria. Debido a la importancia de estos ecosistemas para la reproducción de los flamencos, especialistas del Serfor recorrieron los puntos de anidamiento identificados en los humedales de Sechura . Las acciones forman parte de las labores de vigilancia y seguimiento de la fauna silvestre en Piura. ¿Por qué se refuerza la vigilancia en Sechura? El seguimiento de los flamencos representa un desafío debido a la extensión del territorio y a las características de los humedales. A ello se suma que estas aves no necesariamente utilizan los mismos lugares para construir sus nidos cada año. Por esa razón, los especialistas deben realizar recorridos periódicos para localizar las zonas donde las aves se concentran durante su periodo reproductivo y verificar que no existan situaciones que puedan afectar a los ejemplares. El especialista en fauna silvestre del Serfor, Max Guerra, señaló que es necesario fortalecer las acciones de patrullaje y monitoreo en los espacios de anidamiento, tomando en cuenta tanto las condiciones del territorio como las amenazas que pueden afectar a estas aves. En las intervenciones realizadas en la provincia participaron representantes del Serfor sede Piura , la Fiscalía Especializada en Materia Ambiental de Piura y la Unidad Desconcentrada de Protección de Medio Ambiente de la Policía Nacional del Perú. El trabajo conjunto resulta especialmente importante en una zona donde ya se han registrado casos de afectación a estas aves. En julio de 2025, el Serfor constató la caza ilegal de crías de flamencos chilenos en la laguna del sector La Huaquilla, en Sechura, luego de recibir una alerta. Los especialistas encontraron patas y plumas de polluelos en el lugar. El ciclo reproductivo de los flamencos en Sechura La reproducción de los flamencos chilenos sigue un proceso que se desarrolla durante varios meses. En los humedales de Sechura , la temporada comienza aproximadamente a mediados de abril, cuando las aves empiezan a construir sus nidos. Entre mayo y junio ocurre la postura de los huevos, mientras que durante julio aparecen los primeros polluelos. A partir de la primera semana de agosto, las crías comienzan a desplazarse, una etapa que requiere especial atención por parte de quienes realizan el monitoreo. “Es un lugar alejado, hay mucho territorio que recorrer y se necesita prestar atención cuando están los polluelos; los puntos de anidamiento cambian todos los años”, explicó el guardaparque local Pablo Martínez, quien también destacó la coordinación con el Serfor para realizar los recorridos. ¿Dónde se reproducen los flamencos? El Estuario de Virrilá y la laguna La Niña forman parte de los espacios utilizados por estas aves en la costa norte del Perú. El Serfor ya ha documentado en años anteriores procesos reproductivos y trabajos de seguimiento en ambos lugares. En 2022, por ejemplo, la entidad informó sobre el nacimiento de alrededor de 700 pichones de flamenco chileno en el Estuario de Virrilá. El lugar fue reconocido además como Sitio Ramsar en 2021, debido a su importancia como humedal de relevancia internacional. Un año después, en agosto de 2023, el Serfor realizó el anillamiento de 183 polluelos nacidos en la laguna La Niña. Esta práctica permite identificar a los ejemplares y obtener información sobre sus desplazamientos y los lugares que utilizan durante su vida. El flamenco chileno es una especie migratoria El flamenco chileno utiliza diferentes cuerpos de agua a lo largo de su distribución. Según el Serfor, puede encontrarse en lagunas poco profundas de agua dulce y salada, desde la costa hasta zonas ubicadas a unos 4.800 metros de altitud. Su distribución comprende territorios desde Chile hasta Ecuador , por lo que los ejemplares que nacen en los humedales de Sechura pueden desplazarse posteriormente hacia otras zonas del país o incluso hacia territorios de países vecinos. El anillamiento se ha convertido en una herramienta para conocer mejor estos movimientos. Los registros realizados por especialistas y observadores de aves permiten identificar ejemplares en diferentes puntos y reconstruir parte de sus rutas de desplazamiento. De acuerdo con el Serfor, la especie está clasificada como “Casi Amenazada” . Entre las principales amenazas identificadas figuran la caza ilegal y la degradación de sus hábitats. ¿Qué amenazas enfrentan los flamencos de Sechura? La ubicación alejada de los humedales no elimina los riesgos para estas aves. La caza, la captura y el consumo de fauna silvestre son prácticas que pueden afectar directamente a las poblaciones de flamencos, especialmente durante la temporada en la que permanecen concentrados en las zonas de reproducción. La dificultad para acceder a determinados sectores también obliga a reforzar la vigilancia. Los recorridos permiten identificar nuevos puntos de anidamiento y detectar posibles casos de afectación antes de que el impacto sea mayor. El antecedente de 2025 en La Huaquilla muestra la necesidad de mantener una presencia constante en estos espacios. Para el Serfor, la protección de las áreas donde se reproducen y alimentan las aves requiere coordinación entre autoridades, especialistas y comunidades locales. ¿Cómo reportar un flamenco en situación de riesgo? La ciudadanía puede comunicar al Serfor cualquier caso relacionado con fauna silvestre que se encuentre herida, enferma, fuera de su hábitat o que requiera evaluación e intervención. Según el canal oficial Alerta SERFOR , los ciudadanos deben enviar un mensaje escrito al WhatsApp 947 588 269 , explicando qué ocurrió, dónde se produjo el hecho y cuándo fue observado. También se deben adjuntar fotografías, videos o información de ubicación que ayude a los especialistas a identificar el lugar y evaluar la situación. El Serfor precisa que este canal recibe mensajes escritos y no llamadas telefónicas . Los reportes son derivados a las Administraciones Técnicas Forestales y de Fauna Silvestre según el ámbito correspondiente.</t>
+          <t>Diferentes informes de las oficinas de control institucional del Programa Nacional de Saneamiento Urbano (PNSU) dan cuenta del estado de abandono en su mantenimiento de los Sistemas Alternativos de Recolección y Evacuación de aguas de lluvia (SARE) que se habilitaron en Piura y que costaron millones de soles. Un ejemplo es lo que ocurre en el SARE Cinco Esquinas que costó más de 28 millones de soles, pero ni siquiera tiene un cerco perimétrico para proteger los costosos equipos instalados a pesar de los años pasados. “El grupo electrógeno y la electrobomba constituyen equipos necesarios para el funcionamiento del sistema de bombeo y la evacuación, por lo que su exposición en un área sin control físico permanente de acceso podría afectar su seguridad, conservación y disponibilidad cuando sean requeridos para la operación del SARE”, se lee en el informe de control. De otro lado, el SARE de Ignacio Merino, valorizado en 15 millones de soles, también tiene problemas de falta de mantenimiento. “La falta de culminación de la transferencia legal integral y la ausencia de un marco procedimental que regule las obligaciones de custodia operativa provisoria han provocado que un sistema pluvial de gran inversión (S/ 17.1 millones) no registre ningún tipo de mantenimiento preventivo sobre sus componentes críticos. Esto neutraliza la capacidad de respuesta instalada para salvaguardar a las urbanizaciones del distrito de Piura”, se indica en el documento de Contraloría. Entre las principales observaciones se tiene la acumulación de sedimentos en canaletas cunetas de las vías.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/refuerzan-la-vigilancia-de-flamencos-en-humedales-de-sechura/</t>
+          <t>https://eltiempo.pe/local/los-sare-siguen-sin-mantenimiento-para-funcionar-durante-las-lluvias/</t>
         </is>
       </c>
     </row>
@@ -1013,17 +1052,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Los SARE siguen sin mantenimiento para funcionar durante las lluvias</t>
+          <t>Refuerzan la vigilancia de flamencos en humedales de Sechura</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Diferentes informes de las oficinas de control institucional del Programa Nacional de Saneamiento Urbano (PNSU) dan cuenta del estado de abandono en su mantenimiento de los Sistemas Alternativos de Recolección y Evacuación de aguas de lluvia (SARE) que se habilitaron en Piura y que costaron millones de soles. Un ejemplo es lo que ocurre en el SARE Cinco Esquinas que costó más de 28 millones de soles, pero ni siquiera tiene un cerco perimétrico para proteger los costosos equipos instalados a pesar de los años pasados. “El grupo electrógeno y la electrobomba constituyen equipos necesarios para el funcionamiento del sistema de bombeo y la evacuación, por lo que su exposición en un área sin control físico permanente de acceso podría afectar su seguridad, conservación y disponibilidad cuando sean requeridos para la operación del SARE”, se lee en el informe de control. De otro lado, el SARE de Ignacio Merino, valorizado en 15 millones de soles, también tiene problemas de falta de mantenimiento. “La falta de culminación de la transferencia legal integral y la ausencia de un marco procedimental que regule las obligaciones de custodia operativa provisoria han provocado que un sistema pluvial de gran inversión (S/ 17.1 millones) no registre ningún tipo de mantenimiento preventivo sobre sus componentes críticos. Esto neutraliza la capacidad de respuesta instalada para salvaguardar a las urbanizaciones del distrito de Piura”, se indica en el documento de Contraloría. Entre las principales observaciones se tiene la acumulación de sedimentos en canaletas cunetas de las vías.</t>
+          <t>Unos 4.800 flamencos chilenos ( Phoenicopterus chilensis ) habrían completado este año su etapa de reproducción y desplazamiento en el Estuario de Virrilá y la laguna La Niña , dos importantes humedales ubicados en la provincia de Sechura , en Piura. El registro fue recogido por el Servicio Nacional Forestal y de Fauna Silvestre (Serfor) , organismo adscrito al Ministerio de Desarrollo Agrario y Riego (Midagri), durante las labores de monitoreo de esta especie migratoria. Debido a la importancia de estos ecosistemas para la reproducción de los flamencos, especialistas del Serfor recorrieron los puntos de anidamiento identificados en los humedales de Sechura . Las acciones forman parte de las labores de vigilancia y seguimiento de la fauna silvestre en Piura. ¿Por qué se refuerza la vigilancia en Sechura? El seguimiento de los flamencos representa un desafío debido a la extensión del territorio y a las características de los humedales. A ello se suma que estas aves no necesariamente utilizan los mismos lugares para construir sus nidos cada año. Por esa razón, los especialistas deben realizar recorridos periódicos para localizar las zonas donde las aves se concentran durante su periodo reproductivo y verificar que no existan situaciones que puedan afectar a los ejemplares. El especialista en fauna silvestre del Serfor, Max Guerra, señaló que es necesario fortalecer las acciones de patrullaje y monitoreo en los espacios de anidamiento, tomando en cuenta tanto las condiciones del territorio como las amenazas que pueden afectar a estas aves. En las intervenciones realizadas en la provincia participaron representantes del Serfor sede Piura , la Fiscalía Especializada en Materia Ambiental de Piura y la Unidad Desconcentrada de Protección de Medio Ambiente de la Policía Nacional del Perú. El trabajo conjunto resulta especialmente importante en una zona donde ya se han registrado casos de afectación a estas aves. En julio de 2025, el Serfor constató la caza ilegal de crías de flamencos chilenos en la laguna del sector La Huaquilla, en Sechura, luego de recibir una alerta. Los especialistas encontraron patas y plumas de polluelos en el lugar. El ciclo reproductivo de los flamencos en Sechura La reproducción de los flamencos chilenos sigue un proceso que se desarrolla durante varios meses. En los humedales de Sechura , la temporada comienza aproximadamente a mediados de abril, cuando las aves empiezan a construir sus nidos. Entre mayo y junio ocurre la postura de los huevos, mientras que durante julio aparecen los primeros polluelos. A partir de la primera semana de agosto, las crías comienzan a desplazarse, una etapa que requiere especial atención por parte de quienes realizan el monitoreo. “Es un lugar alejado, hay mucho territorio que recorrer y se necesita prestar atención cuando están los polluelos; los puntos de anidamiento cambian todos los años”, explicó el guardaparque local Pablo Martínez, quien también destacó la coordinación con el Serfor para realizar los recorridos. ¿Dónde se reproducen los flamencos? El Estuario de Virrilá y la laguna La Niña forman parte de los espacios utilizados por estas aves en la costa norte del Perú. El Serfor ya ha documentado en años anteriores procesos reproductivos y trabajos de seguimiento en ambos lugares. En 2022, por ejemplo, la entidad informó sobre el nacimiento de alrededor de 700 pichones de flamenco chileno en el Estuario de Virrilá. El lugar fue reconocido además como Sitio Ramsar en 2021, debido a su importancia como humedal de relevancia internacional. Un año después, en agosto de 2023, el Serfor realizó el anillamiento de 183 polluelos nacidos en la laguna La Niña. Esta práctica permite identificar a los ejemplares y obtener información sobre sus desplazamientos y los lugares que utilizan durante su vida. El flamenco chileno es una especie migratoria El flamenco chileno utiliza diferentes cuerpos de agua a lo largo de su distribución. Según el Serfor, puede encontrarse en lagunas poco profundas de agua dulce y salada, desde la costa hasta zonas ubicadas a unos 4.800 metros de altitud. Su distribución comprende territorios desde Chile hasta Ecuador , por lo que los ejemplares que nacen en los humedales de Sechura pueden desplazarse posteriormente hacia otras zonas del país o incluso hacia territorios de países vecinos. El anillamiento se ha convertido en una herramienta para conocer mejor estos movimientos. Los registros realizados por especialistas y observadores de aves permiten identificar ejemplares en diferentes puntos y reconstruir parte de sus rutas de desplazamiento. De acuerdo con el Serfor, la especie está clasificada como “Casi Amenazada” . Entre las principales amenazas identificadas figuran la caza ilegal y la degradación de sus hábitats. ¿Qué amenazas enfrentan los flamencos de Sechura? La ubicación alejada de los humedales no elimina los riesgos para estas aves. La caza, la captura y el consumo de fauna silvestre son prácticas que pueden afectar directamente a las poblaciones de flamencos, especialmente durante la temporada en la que permanecen concentrados en las zonas de reproducción. La dificultad para acceder a determinados sectores también obliga a reforzar la vigilancia. Los recorridos permiten identificar nuevos puntos de anidamiento y detectar posibles casos de afectación antes de que el impacto sea mayor. El antecedente de 2025 en La Huaquilla muestra la necesidad de mantener una presencia constante en estos espacios. Para el Serfor, la protección de las áreas donde se reproducen y alimentan las aves requiere coordinación entre autoridades, especialistas y comunidades locales. ¿Cómo reportar un flamenco en situación de riesgo? La ciudadanía puede comunicar al Serfor cualquier caso relacionado con fauna silvestre que se encuentre herida, enferma, fuera de su hábitat o que requiera evaluación e intervención. Según el canal oficial Alerta SERFOR , los ciudadanos deben enviar un mensaje escrito al WhatsApp 947 588 269 , explicando qué ocurrió, dónde se produjo el hecho y cuándo fue observado. También se deben adjuntar fotografías, videos o información de ubicación que ayude a los especialistas a identificar el lugar y evaluar la situación. El Serfor precisa que este canal recibe mensajes escritos y no llamadas telefónicas . Los reportes son derivados a las Administraciones Técnicas Forestales y de Fauna Silvestre según el ámbito correspondiente.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/los-sare-siguen-sin-mantenimiento-para-funcionar-durante-las-lluvias/</t>
+          <t>https://eltiempo.pe/local/refuerzan-la-vigilancia-de-flamencos-en-humedales-de-sechura/</t>
         </is>
       </c>
     </row>
@@ -1134,21 +1173,21 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>46272</v>
+        <v>46273</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>I.E. San Ramón de Chulucanas se consagra campeona del Regional Singing Festival 2026</t>
+          <t>Dren Maldonado: MTC enviará puente a Piura tras alerta por riesgo de dejar incomunicadas a 60 mil personas</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>La Institución Educativa San Ramón de Chulucanas, representante de la UGEL Chulucanas , obtuvo el primer lugar en el Regional Singing Festival 2026 “Singing for a Better World”, organizado por la Dirección Regional de Educación de Piura. PUEDES LEER ► Sobrevive tras 10 días sepultada por el lodo y es rescatada cuando su familia ya la había dado por muerta La actividad se desarrolló en el parque Néstor Martos de Piura y reunió a estudiantes representantes de las 12 UGEL de la región, quienes demostraron sus habilidades en la interpretación de canciones en inglés. El festival tiene como finalidad fortalecer las competencias comunicativas en el idioma inglés, además de promover la creatividad, la expresión artística y la participación de los estudiantes. La iniciativa se desarrolla en concordancia con el Currículo Nacional de la Educación Básica. Durante sus presentaciones, los participantes también transmitieron mensajes relacionados con valores y actitudes que contribuyen a una convivencia democrática, respetuosa, inclusiva y solidaria. San Ramón conquistó el primer lugar La IE San Ramón logró imponerse en la competencia con la interpretación de la canción “Hand for Chulucanas”, presentación que le permitió quedarse con el primer puesto del festival regional. El segundo lugar fue para la IE Libertadores de América, representante de la UGEL La Unión, que participó con la canción “The Song of Tomorrow”. Mientras que el tercer puesto correspondió a la IE César Vallejo, de la UGEL Morropón, con la interpretación de “Brighter Than Before”. La competencia comenzó en cada institución educativa y posteriormente continuó en las diferentes etapas de las 12 UGEL de Piura: Ayabaca, Chulucanas, Huancabamba, Huarmaca, La Unión, Morropón, Paita, Piura, Sechura, Sullana, Talara y Tambogrande. Además de impulsar el aprendizaje del inglés, el festival busca fortalecer la sana competencia, el trabajo en equipo y la integración entre estudiantes de diferentes provincias de la región.</t>
+          <t>La senadora por Piura, Karla Schaefer, informó que el ministro de Transportes y Comunicaciones, Rafael Rey Rey, dispuso el envío de un puente que será utilizado para garantizar la conexión vial ante una eventual afectación del dren Maldonado. Puedes Leer | El Niño superaría al de 1998 y traería impactos “insospechados” en la región Piura La situación de riesgo en el dren Maldonado, en el distrito de Veintiséis de Octubre, habría encontrado una respuesta desde el Gobierno central. La senadora por Piura, Karla Schaefer , informó que el Ministerio de Transportes y Comunicaciones (MTC) dispuso el envío de un puente para atender una eventual interrupción de la vía en este sector. Según explicó Schaefer, el pedido fue trasladado al MTC debido a la preocupación por la seguridad de la red vial y el riesgo de que una eventual afectación del dren Maldonado pueda comprometer la comunicación de importantes sectores de Piura. “ El ministro de Transportes y Comunicaciones, Rafael Rey, afirmó que él va a poner el puente ”, señaló la senadora. Schaefer explicó que inicialmente se realizaron consultas tanto al MTC como al Ministerio de Defensa (Mindef), a través de la empresa estatal SIMA Perú , para evaluar una alternativa que permita responder ante una emergencia. Sin embargo, de acuerdo con la parlamentaria, el ministro Rey tomó la decisión de disponer directamente la estructura tras conocer la situación. “Se había hecho la consulta al Ministerio de Transportes y Comunicaciones y al Ministerio de Defensa a través de SIMA Perú. Pero el ministro Rafael Rey, gracias a la delegación de facultades, ni bien vio el tema, dijo: ‘ Yo voy a dar ese puente ’”, declaró. Puente será trasladado a Piura La senadora informó además que la estructura ya habría salido de Lima con destino a Piura y será almacenada temporalmente en Piura Futura , desde donde podrá ser trasladada hacia los puntos que requieran atención. “Hoy han salido de Lima y serán almacenados en Piura Futura para que desde ahí se vayan a varios puntos”, indicó Schaefer. La medida busca contar con una alternativa de conexión ante una eventual emergencia relacionada con el dren Maldonado, especialmente considerando el riesgo advertido para la población de Veintiséis de Octubre. En declaraciones difundidas previamente por El Tiempo , Schaefer había advertido que una eventual afectación del dren podría dejar incomunicadas a unas 60 mil personas y había cuestionado las dificultades generadas por la distribución de competencias entre distintas instituciones del Estado. Schaefer agradece respuesta del MTC La senadora destacó la rapidez con la que, según su versión, el ministro de Transportes habría atendido el pedido. “ Agradecerle al ministro esa eficiencia en solucionar ese problema en que se prioriza la vida ”, manifestó. Asimismo, reconoció el trabajo del director de Puentes, Julio Palacios , y de la Municipalidad Distrital de Veintiséis de Octubre , instituciones que, según indicó, tendrán participación en la gestión relacionada con la estructura. Mira También | ¡Ni los niños se salvan del hampa! Delincuentes saquean colegio y se llevan hasta los juguetes en el Bajo Piura El dren Maldonado es uno de los puntos críticos del sistema de drenaje de Veintiséis de Octubre. En febrero de 2026, el INDECI ya había identificado la necesidad de gestionar requerimientos para garantizar su operatividad, debido a su importancia para la evacuación de aguas pluviales durante lluvias intensas. La atención al dren Maldonado forma parte de una problemática mayor de infraestructura y prevención frente a lluvias en Piura, donde distintas autoridades han advertido sobre la necesidad de acelerar las intervenciones antes de que se presenten emergencias.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/i-e-san-ramon-de-chulucanas-se-consagra-campeona-del-regional-singing-festival-2026/</t>
+          <t>https://eltiempo.pe/local/dren-maldonado-mtc-enviara-puente-a-piura-tras-alerta-por-riesgo-de-dejar-incomunicadas-a-60-mil-personas/</t>
         </is>
       </c>
     </row>
@@ -1163,17 +1202,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Así van los candidatos a falta de un mes para elecciones</t>
+          <t>I.E. San Ramón de Chulucanas se consagra campeona del Regional Singing Festival 2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ICSI Perú hizo una encuesta y revela cómo van las preferencias de los piuranos sobre su próximo gobernador y alcaldes. PUEDES LEER ► Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba Las elecciones regionales y municipales están a la vuelta de la esquina y lo único seguro es que sí o sí habrá una segunda vuelta para el cargo de gobernador regional. De acuerdo a ley, si ninguna lista supera el 30% de votos válidos, se convoca a una segunda vuelta entre los dos primeros del escrutinio. De acuerdo a la última encuesta de la empresa ICSI Perú ninguno de los aspirantes a la máxima autoridad regional llega al 30% de las preferencias. Según el estudio de opinión pública, el primer lugar es para el exgobernador Reynaldo Hilbck (Alianza para el Progreso) con 22.5%; seguido por Santiago Paz (Somos Perú) con 13.7% ; Mártires Lizana (Fuerza Popular) con 11.1% y Guillermo La Torre (Podemos Perú) con 10.9%. En el caso de los candidatos provinciales, la disputa parece más reñida y la diferencia de porcentajes es más ajustada entre los aspirantes, con lo cual la campaña de aquí hasta el domingo 4 de octubre será una competencia voto a voto y de convencimiento de los indecisos. Gobierno Regional Sobre el tema, el gerente de ICSI Perú, Mauro Vegas Carmen , consideró que uno de los factores del respaldo a Hilbck son sus candidatos en las provincias con mayor caudal electoral de votos. “En los resultados de los 27 distritos a donde se ha ido, Hilbck alcanza la mayor votación en Piura, Veintiséis de Octubre, Catacaos, Sullana, Morropón, Chulucanas, Talara, Órganos y otros. Todo eso le da ese porcentaje que ahora ha sacado frente al segundo. Por ejemplo, en Piura tiene 19.66% y Somos Perú tiene 15.33%; en Castilla, Hilbck tiene 13.60% y Somos Perú unos 10.90% y en Veintiséis de Octubre, Hilbck tiene 20.35% y Somos Perú, 15.34%. En Sullana que es una plaza fuerte, se tiene 19.59% y Santiago Paz llega a 12.14%, asimismo, en Chulucanas, Hilbck logra 17.4% y Somos Perú 9.87%”, mencionó. Agrega que este respaldo de Hilbck en las provincias y distritos se refleja en sus candidatos para estas jurisdicciones. Un segundo factor, sostiene, es el respaldo de la maquinaria electoral de un partido como Alianza para el Progreso (APP). “Ese porcentaje es coherente porque sus candidatos provinciales y también distritales ganan, además que la maquinaria electoral que se percibe en la región”, agregó. Somos Perú Sobre Santiago Paz de Somos Perú que marcha en segundo lugar con 13.7%, el gerente de ICSI Perú sostuvo que no le va bien con sus candidatos en Piura, Castilla, Veintiséis de Octubre, Tambogrande o Sullana. “En el caso Chulucanas, como distrito capital, el candidato Nelson Mío que hace un mes era fuerte, ha tenido un descenso porque ahí han ingresado candidatos nuevos como Hernán Pasapera de Renovación y Manuel Cueva de Podemos. Eso le ha restado fuerza a Somos Perú”, aseveró. Sobre Mártires Lizana de Fuerza Popular que marcha tercero, Vegas destaca que esto ocurre por la aceptación del candidato a la provincia de Piura, Martín Olivares, que está segundo en la preferencial provincial. Nulos En el estudio también se revela que un 18% de los encuestados no votaría por ninguno de los postulantes o lo haría en blanco. “Esto puede variar producto de la campaña y contracampaña. Aquí quien tiene mejor equipo de contracampaña es el que tiene mayor ventaja de ganar. Es quien reacciona rápido, de forma contundente y demoledora. No siempre la percepción es la verdad, por eso una contracampaña tiene que responderse de manera rápida y contundente. No se trata del mejor indudablemente, sino de quien cometa menos errores y sepa responder a los ataques fundados o infundados”, destacó.n</t>
+          <t>La Institución Educativa San Ramón de Chulucanas, representante de la UGEL Chulucanas , obtuvo el primer lugar en el Regional Singing Festival 2026 “Singing for a Better World”, organizado por la Dirección Regional de Educación de Piura. PUEDES LEER ► Sobrevive tras 10 días sepultada por el lodo y es rescatada cuando su familia ya la había dado por muerta La actividad se desarrolló en el parque Néstor Martos de Piura y reunió a estudiantes representantes de las 12 UGEL de la región, quienes demostraron sus habilidades en la interpretación de canciones en inglés. El festival tiene como finalidad fortalecer las competencias comunicativas en el idioma inglés, además de promover la creatividad, la expresión artística y la participación de los estudiantes. La iniciativa se desarrolla en concordancia con el Currículo Nacional de la Educación Básica. Durante sus presentaciones, los participantes también transmitieron mensajes relacionados con valores y actitudes que contribuyen a una convivencia democrática, respetuosa, inclusiva y solidaria. San Ramón conquistó el primer lugar La IE San Ramón logró imponerse en la competencia con la interpretación de la canción “Hand for Chulucanas”, presentación que le permitió quedarse con el primer puesto del festival regional. El segundo lugar fue para la IE Libertadores de América, representante de la UGEL La Unión, que participó con la canción “The Song of Tomorrow”. Mientras que el tercer puesto correspondió a la IE César Vallejo, de la UGEL Morropón, con la interpretación de “Brighter Than Before”. La competencia comenzó en cada institución educativa y posteriormente continuó en las diferentes etapas de las 12 UGEL de Piura: Ayabaca, Chulucanas, Huancabamba, Huarmaca, La Unión, Morropón, Paita, Piura, Sechura, Sullana, Talara y Tambogrande. Además de impulsar el aprendizaje del inglés, el festival busca fortalecer la sana competencia, el trabajo en equipo y la integración entre estudiantes de diferentes provincias de la región.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/asi-van-los-candidatos-a-falta-de-un-mes-para-elecciones/</t>
+          <t>https://eltiempo.pe/local/i-e-san-ramon-de-chulucanas-se-consagra-campeona-del-regional-singing-festival-2026/</t>
         </is>
       </c>
     </row>
@@ -1188,17 +1227,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba</t>
+          <t>Así van los candidatos a falta de un mes para elecciones</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Unos 12 pasajeros se salvaron de caer a un abismo de aproximadamente 200 metros luego de que una miniván de una empresa de transporte sufriera un accidente en la carretera Canchaque-Huancabamba, en el sector Las Minas. Según información preliminar, la unidad terminó volcada y quedó peligrosamente cerca del precipicio, generando momentos de angustia entre los pasajeros, entre ellos algunos menores de edad, quienes temieron lo peor. Pese a la violencia del accidente, los ocupantes solo habrían sufrido algunos golpes, además del fuerte susto provocado por el incidente. Hasta el momento no se han reportado oficialmente personas con lesiones de consideración. EL EQUIPAJE El accidente también ocasionó la caída de algunos equipajes que eran transportados en la parte superior de la miniván, los cuales algunos habrían terminado en el fondo del abismo. De acuerdo con versiones preliminares, no se descarta que el vehículo haya sufrido algún desperfecto mecánico antes de producirse el accidente. Sin embargo, esta posibilidad deberá ser determinada mediante las investigaciones correspondientes. Asimismo, las autoridades realizan las diligencias para establecer las causas exactas del siniestro y determinar las condiciones en las que circulaba la unidad. Cabe mencionar que el hecho vuelve a poner en evidencia el peligro de transitar por esta vía, caracterizada por sus pronunciadas pendientes y zonas de profundo precipicio.</t>
+          <t>ICSI Perú hizo una encuesta y revela cómo van las preferencias de los piuranos sobre su próximo gobernador y alcaldes. PUEDES LEER ► Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba Las elecciones regionales y municipales están a la vuelta de la esquina y lo único seguro es que sí o sí habrá una segunda vuelta para el cargo de gobernador regional. De acuerdo a ley, si ninguna lista supera el 30% de votos válidos, se convoca a una segunda vuelta entre los dos primeros del escrutinio. De acuerdo a la última encuesta de la empresa ICSI Perú ninguno de los aspirantes a la máxima autoridad regional llega al 30% de las preferencias. Según el estudio de opinión pública, el primer lugar es para el exgobernador Reynaldo Hilbck (Alianza para el Progreso) con 22.5%; seguido por Santiago Paz (Somos Perú) con 13.7% ; Mártires Lizana (Fuerza Popular) con 11.1% y Guillermo La Torre (Podemos Perú) con 10.9%. En el caso de los candidatos provinciales, la disputa parece más reñida y la diferencia de porcentajes es más ajustada entre los aspirantes, con lo cual la campaña de aquí hasta el domingo 4 de octubre será una competencia voto a voto y de convencimiento de los indecisos. Gobierno Regional Sobre el tema, el gerente de ICSI Perú, Mauro Vegas Carmen , consideró que uno de los factores del respaldo a Hilbck son sus candidatos en las provincias con mayor caudal electoral de votos. “En los resultados de los 27 distritos a donde se ha ido, Hilbck alcanza la mayor votación en Piura, Veintiséis de Octubre, Catacaos, Sullana, Morropón, Chulucanas, Talara, Órganos y otros. Todo eso le da ese porcentaje que ahora ha sacado frente al segundo. Por ejemplo, en Piura tiene 19.66% y Somos Perú tiene 15.33%; en Castilla, Hilbck tiene 13.60% y Somos Perú unos 10.90% y en Veintiséis de Octubre, Hilbck tiene 20.35% y Somos Perú, 15.34%. En Sullana que es una plaza fuerte, se tiene 19.59% y Santiago Paz llega a 12.14%, asimismo, en Chulucanas, Hilbck logra 17.4% y Somos Perú 9.87%”, mencionó. Agrega que este respaldo de Hilbck en las provincias y distritos se refleja en sus candidatos para estas jurisdicciones. Un segundo factor, sostiene, es el respaldo de la maquinaria electoral de un partido como Alianza para el Progreso (APP). “Ese porcentaje es coherente porque sus candidatos provinciales y también distritales ganan, además que la maquinaria electoral que se percibe en la región”, agregó. Somos Perú Sobre Santiago Paz de Somos Perú que marcha en segundo lugar con 13.7%, el gerente de ICSI Perú sostuvo que no le va bien con sus candidatos en Piura, Castilla, Veintiséis de Octubre, Tambogrande o Sullana. “En el caso Chulucanas, como distrito capital, el candidato Nelson Mío que hace un mes era fuerte, ha tenido un descenso porque ahí han ingresado candidatos nuevos como Hernán Pasapera de Renovación y Manuel Cueva de Podemos. Eso le ha restado fuerza a Somos Perú”, aseveró. Sobre Mártires Lizana de Fuerza Popular que marcha tercero, Vegas destaca que esto ocurre por la aceptación del candidato a la provincia de Piura, Martín Olivares, que está segundo en la preferencial provincial. Nulos En el estudio también se revela que un 18% de los encuestados no votaría por ninguno de los postulantes o lo haría en blanco. “Esto puede variar producto de la campaña y contracampaña. Aquí quien tiene mejor equipo de contracampaña es el que tiene mayor ventaja de ganar. Es quien reacciona rápido, de forma contundente y demoledora. No siempre la percepción es la verdad, por eso una contracampaña tiene que responderse de manera rápida y contundente. No se trata del mejor indudablemente, sino de quien cometa menos errores y sepa responder a los ataques fundados o infundados”, destacó.n</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/minivan-queda-al-borde-de-un-abismo-en-la-carretera-canchaque-huancabamba/</t>
+          <t>https://eltiempo.pe/local/asi-van-los-candidatos-a-falta-de-un-mes-para-elecciones/</t>
         </is>
       </c>
     </row>
@@ -1213,17 +1252,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Choque de autos derriba poste</t>
+          <t>Fiesta termina con una mujer fallecida</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Un violento accidente de tránsito entre dos automóviles se registró ayer en horas de la mañana en la avenida Universitaria de Piura, a la altura del Fundo Vite. PUEDES LEER ► “Monstruo de las 10 cabezas” Según información preliminar, uno de los vehículos tras el choque habría también impactado contra un poste que no sería de tendido eléctrico, provocando que la estructura se desplomara y terminara cayendo sobre el otro automóvil. Los vehículos permanecieron en la zona del accidente, mientras efectivos de la Policía Nacional acudieron para realizar las diligencias correspondientes y determinar las circunstancias en que ocurrió el hecho. Hasta el cierre de edición, no se informó oficialmente sobre personas heridas como consecuencia del accidente. Cabe mencionar que el accidente generó preocupación entre los conductores que transitaban por este importante tramo de la avenida Universitaria.</t>
+          <t>Una fiesta terminó en tragedia en la urbanización Las Casuarinas II Etapa, en el distrito Veintiséis de Octubre , luego de que una joven de nacionalidad colombiana perdiera la vida tras caer desde un tragaluz del tercer piso de un inmueble hacia el segundo nivel. La víctima fue identificada como Juliet Alisson Zambrano Fino, de 21 años de edad. PUEDES LEER ► FEN asusta a la banca privada El hecho ocurrió durante una reunión social y las circunstancias de la caída son materia de investigación por parte de la Policía. De acuerdo con información preliminar, una de las hipótesis que manejan las autoridades es que la joven habría sido presuntamente arrojada por un tragaluz, desde donde terminó cayendo hasta el segundo piso del inmueble. Sin embargo, esta versión todavía deberá ser corroborada mediante las diligencias policiales, pericias y demás elementos que permitan determinar qué ocurrió exactamente antes de la caída. SIN SIGNOS VITALES Tras conocerse el hecho, personal de Serenazgo del distrito Veintiséis de Octubre y una ambulancia del SAMU Piura llegaron hasta el lugar de la tragedia para brindar atención a la víctima. No obstante, los equipos de emergencia encontraron a la joven sin signos vitales. En el lugar también se encontraba un ciudadano extranjero, quien, visiblemente afectado y entre lágrimas, solicitaba ayuda para la mujer. RECOPILAN INFORMACIÓN Agentes de la Policía Nacional acudieron posteriormente a la escena para realizar las primeras diligencias, verificar las condiciones del inmueble y recopilar información que permita reconstruir los momentos previos y posteriores al fatal incidente. Las autoridades deberán determinar si la caída se produjo accidentalmente o si existió la intervención de otra persona. Para ello, se vienen recogiendo testimonios de quiénes participaron en la fiesta y de otros posibles testigos, además de realizarse las pericias correspondientes. El cuerpo de Juliet Alisson Zambrano Fino fue trasladado a la morgue de Piura, donde se realizarán los procedimientos establecidos por ley. INVESTIGACIONES Mientras avanzan las investigaciones, el caso ha generado preocupación entre los vecinos de Las Casuarinas. La Policía busca establecer las circunstancias exactas de la muerte y, de corresponder, identificar a los responsables y determinar las responsabilidades que establezca la investigación.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/choque-de-autos-derriba-poste/</t>
+          <t>https://eltiempo.pe/local/fiesta-termina-con-una-mujer-fallecida/</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1277,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FEN asusta a la banca privada</t>
+          <t>Choque de autos derriba poste</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>El impacto del Fenómeno El Niño (FEN) en el terreno económico también se sentirá en los créditos a las pequeñas y medianas empresas relacionadas a los sectores primarios de la economía como son la pesca y agricultura. PUEDES LEER ► ProInversión y Marina de Guerra evaluarán proyectos de inversión privada sobre terrenos y bienes navales De acuerdo a los especialistas consultados, algunas empresas financieras podrían reforzar sus criterios para el otorgamiento de préstamos a los pequeños empresarios, con la finalidad de prevenir problemas de morosidad. “Los créditos asociados a personas que se desempeñan en esos sectores van a tener probablemente dificultades para afrontar sus deudas. Eso es algo que ya vimos en períodos pasados del FEN como en el 2023 y 2017” , comentó Stephani Maita, economista senior del Instituto Peruano de Economía (IPE). Explica que el impacto del FEN en el agro y pesca se relaciona en un primer momento con la pérdida del empleo. “Un tercio del empleo total en la región está vinculado al sector agrícola entonces las familias que tengan actividades vinculadas a este sector y tengan préstamos probablemente van a tener dificultades para afrontar sus deudas. Lo mismo con las empresas. A esto también se va el efecto por los precios al alza. Potencialmente podría terminar afectando la calidad de las carteras de créditos ”, enfatizó. Expectativas De otro lado, Maita señala que pese a la amenaza del fenómeno natural que se avecina, todavía hay expectativas positivas en la economía nacional. “El Banco Central de Reserva publicó una encuesta de perspectivas sobre el mercado de créditos tanto desde el lado de la oferta, es decir la perspectiva de los bancos y entidades financieras, como desde la demanda que es más desde los usuarios que solicitan los créditos. Por el lado de la demanda se encontraba que la perspectiva era favorable en la medida que la actividad económica en general, mas allá de los sectores primarios, goza de salud y está creciendo de forma importante”, aseveró Maita. Sin embargo, por el lado de las empresas existe un mayo grado de cautela sobre a quién le otorgan los préstamos con la finalidad de evitar el aumento de la morosidad. “Las empresas ya están previendo reforzar algunos criterios para otorgar créditos considerando los eventos climáticos que van a afectar, probablemente, en mayor medida los segmentos de las carteras más pequeñas, hablamos de microempresas, medianas y pequeñas empresas, las cuales son las que han registrado las mayores dificultades para afrontar sus créditos en el pasado”, manifestó Maita. Criterios Desde su punto de vista los nuevos requisitos implica un examen más exhaustivo del cliente que llega a solicitar el financiamiento. “Se refiere a otorgar créditos de menor tamaño, con plazos más extensos para que las cuotas sean un poco más pequeñas o quizás hacer una evaluación más minuciosa respecto de los ingresos de las empresas o que tanta exposición tienen a este tipo de fenómenos dependiendo de las actividades en las que se desempeñan. Por ejemplo, una empresa dedicada a la agroexportación probablemente será mucho más golpeada por el fenómeno climático frente a una empresa de transporte. Igual esta última va a sufrir algunos estragos por las lluvias, pero ese impacto es considerablemente menor frente a una empresa que se desempeña en agricultura. Agrega que en este punto los bancos tienden a elegir un poco mejor o cambiar un poco sus decisiones de dación de créditos para evitar exponerse a potenciales impagos.</t>
+          <t>Un violento accidente de tránsito entre dos automóviles se registró ayer en horas de la mañana en la avenida Universitaria de Piura, a la altura del Fundo Vite. PUEDES LEER ► “Monstruo de las 10 cabezas” Según información preliminar, uno de los vehículos tras el choque habría también impactado contra un poste que no sería de tendido eléctrico, provocando que la estructura se desplomara y terminara cayendo sobre el otro automóvil. Los vehículos permanecieron en la zona del accidente, mientras efectivos de la Policía Nacional acudieron para realizar las diligencias correspondientes y determinar las circunstancias en que ocurrió el hecho. Hasta el cierre de edición, no se informó oficialmente sobre personas heridas como consecuencia del accidente. Cabe mencionar que el accidente generó preocupación entre los conductores que transitaban por este importante tramo de la avenida Universitaria.</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/fen-asusta-a-la-banca-privada/</t>
+          <t>https://eltiempo.pe/local/choque-de-autos-derriba-poste/</t>
         </is>
       </c>
     </row>
@@ -1263,17 +1302,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>“Monstruo de las 10 cabezas”</t>
+          <t>FEN asusta a la banca privada</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>En la carrera contra el tiempo para ejecutar las actividades que aminoren el impacto del Fenómeno El Niño (FEN) , la región se enfrenta a otro enemigo. Se trata del propio Estado y la complejidad de sus instituciones, procesos y competencias que hacen mucho más lenta la respuesta a la emergencia. PUEDES LEER ► Callao: joven de 20 años es asesinado a balazos en el distrito de Mi Perú “La situación de desorden que tenemos en el Estado es como decir que tenemos un monstruo de 10 cabezas. Está lo que maneja Veintiséis de Octubre, lo que maneja la Municipalidad de Piura o el Ministerio de Vivienda, cuando debería haber una sola cabeza en el control de inundaciones y de nuestras cuencas [Luego] tenemos el proyecto Alto Piura y el proyecto Chira Piura que manejan la jurisdicción de estas dos cuencas con el ANA (Autoridad Nacional del Agua) como ente rector. [También] tuvimos la Autoridad para la Reconstrucción con Cambios (ARCC) que evaluaba un plan maestro”, aseveró la senadora de Piura, Karla Schaefer. Otra muestra del problema de esta gran burocracia, señala, es que luego se creó la Autoridad Nacional de Infraestructura (ANIN) que también tiene fichas de intervención de diferentes puntos críticos. “Y esas benditas competencias que no te dejan [trabajar] y todos se mueren de miedo de firmar un documento por la Contraloría [...] Por ejemplo, el alcalde de Veintiséis de Octubre tiene una situación compleja con el dren Maldonado y que podría dejar incomunicado a 60 mil personas de un lado a otro. Se pidió el apoyo a Transportes, como una de las alternativas, que tiene puentes Baileys, aún esperamos respuesta. [...] Este es un tema que el decreto de urgencia nos debería dejar actuar y que no permitan que los empresarios, que hace dos semanas están esperando este documento, luego se vean entrampados” , consideró. Reunión Schaefer brindó estas declaraciones este martes en la primera sesión descentralizada del Consejo Directivo Descentralizado Macro Región Norte que agrupa a las empresas asociadas a la Confiep (Confederación Nacional de Instituciones Empresariales Privadas), que desean apoyar a las actividades de mitigación contra El Niño. Parte de este problema también fue expuesto por el presidente de la Confiep, Jorge Zapata , quien destacó que las empresas privadas podrían invertir unos 4 mil millones de sus impuestos en Piura bajo una modalidad abreviada de obras por impuestos Se trata de servicios por impuestos que todavía no existe porque debe aprobarse el decreto supremo para que las empresas privadas tengan marco legal para intervenir en Chutuque, cuencas ciegas u otros puntos críticos. “Pi ura cuenta con 4 mil 352 millones de soles bajo la modalidad de obras o servicios por impuestos. Tenemos la plata y no somos capaces de solucionar los temas. No es un tema de dinero y hace mucho tiempo lo venimos diciendo. Los privados ya están haciendo el esfuerzo necesario; ya hemos visto donaciones de varias empresas; la Sociedad Nacional de Minería está evaluando la apertura del canal de Chutuque, pero hay un detalle mínimo y que parece absurdo, sobre a quién se va a contratar para la información de la ficha técnica [de Chutuque]. Tenemos que ponernos de acuerdo en un detalle mínimo cuando tenemos 18 mil millones de soles por ejecutar”, destacó. Zapata mencionó esto en relación a la ficha técnica que hace falta para intervenir en los 6 kilómetros del canal Chutuque mediante explosivos. La ANA señala que no hay información, mientras que desde la Cámara de Comercio se indica que esta información la posee el ingeniero César Alvarado. Alvarado es el especialista y autor de la primera versión del Plan Integral de Manejo del Río Piura que contrató la desaparecida Autoridad para la Reconstrucción con Cambios (ARCC), la cual nació luego de la inundación del 2017.</t>
+          <t>El impacto del Fenómeno El Niño (FEN) en el terreno económico también se sentirá en los créditos a las pequeñas y medianas empresas relacionadas a los sectores primarios de la economía como son la pesca y agricultura. PUEDES LEER ► ProInversión y Marina de Guerra evaluarán proyectos de inversión privada sobre terrenos y bienes navales De acuerdo a los especialistas consultados, algunas empresas financieras podrían reforzar sus criterios para el otorgamiento de préstamos a los pequeños empresarios, con la finalidad de prevenir problemas de morosidad. “Los créditos asociados a personas que se desempeñan en esos sectores van a tener probablemente dificultades para afrontar sus deudas. Eso es algo que ya vimos en períodos pasados del FEN como en el 2023 y 2017” , comentó Stephani Maita, economista senior del Instituto Peruano de Economía (IPE). Explica que el impacto del FEN en el agro y pesca se relaciona en un primer momento con la pérdida del empleo. “Un tercio del empleo total en la región está vinculado al sector agrícola entonces las familias que tengan actividades vinculadas a este sector y tengan préstamos probablemente van a tener dificultades para afrontar sus deudas. Lo mismo con las empresas. A esto también se va el efecto por los precios al alza. Potencialmente podría terminar afectando la calidad de las carteras de créditos ”, enfatizó. Expectativas De otro lado, Maita señala que pese a la amenaza del fenómeno natural que se avecina, todavía hay expectativas positivas en la economía nacional. “El Banco Central de Reserva publicó una encuesta de perspectivas sobre el mercado de créditos tanto desde el lado de la oferta, es decir la perspectiva de los bancos y entidades financieras, como desde la demanda que es más desde los usuarios que solicitan los créditos. Por el lado de la demanda se encontraba que la perspectiva era favorable en la medida que la actividad económica en general, mas allá de los sectores primarios, goza de salud y está creciendo de forma importante”, aseveró Maita. Sin embargo, por el lado de las empresas existe un mayo grado de cautela sobre a quién le otorgan los préstamos con la finalidad de evitar el aumento de la morosidad. “Las empresas ya están previendo reforzar algunos criterios para otorgar créditos considerando los eventos climáticos que van a afectar, probablemente, en mayor medida los segmentos de las carteras más pequeñas, hablamos de microempresas, medianas y pequeñas empresas, las cuales son las que han registrado las mayores dificultades para afrontar sus créditos en el pasado”, manifestó Maita. Criterios Desde su punto de vista los nuevos requisitos implica un examen más exhaustivo del cliente que llega a solicitar el financiamiento. “Se refiere a otorgar créditos de menor tamaño, con plazos más extensos para que las cuotas sean un poco más pequeñas o quizás hacer una evaluación más minuciosa respecto de los ingresos de las empresas o que tanta exposición tienen a este tipo de fenómenos dependiendo de las actividades en las que se desempeñan. Por ejemplo, una empresa dedicada a la agroexportación probablemente será mucho más golpeada por el fenómeno climático frente a una empresa de transporte. Igual esta última va a sufrir algunos estragos por las lluvias, pero ese impacto es considerablemente menor frente a una empresa que se desempeña en agricultura. Agrega que en este punto los bancos tienden a elegir un poco mejor o cambiar un poco sus decisiones de dación de créditos para evitar exponerse a potenciales impagos.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/monstruo-de-las-10-cabezas/</t>
+          <t>https://eltiempo.pe/local/fen-asusta-a-la-banca-privada/</t>
         </is>
       </c>
     </row>
@@ -1288,17 +1327,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fiesta termina con una mujer fallecida</t>
+          <t>“Monstruo de las 10 cabezas”</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Una fiesta terminó en tragedia en la urbanización Las Casuarinas II Etapa, en el distrito Veintiséis de Octubre , luego de que una joven de nacionalidad colombiana perdiera la vida tras caer desde un tragaluz del tercer piso de un inmueble hacia el segundo nivel. La víctima fue identificada como Juliet Alisson Zambrano Fino, de 21 años de edad. PUEDES LEER ► FEN asusta a la banca privada El hecho ocurrió durante una reunión social y las circunstancias de la caída son materia de investigación por parte de la Policía. De acuerdo con información preliminar, una de las hipótesis que manejan las autoridades es que la joven habría sido presuntamente arrojada por un tragaluz, desde donde terminó cayendo hasta el segundo piso del inmueble. Sin embargo, esta versión todavía deberá ser corroborada mediante las diligencias policiales, pericias y demás elementos que permitan determinar qué ocurrió exactamente antes de la caída. SIN SIGNOS VITALES Tras conocerse el hecho, personal de Serenazgo del distrito Veintiséis de Octubre y una ambulancia del SAMU Piura llegaron hasta el lugar de la tragedia para brindar atención a la víctima. No obstante, los equipos de emergencia encontraron a la joven sin signos vitales. En el lugar también se encontraba un ciudadano extranjero, quien, visiblemente afectado y entre lágrimas, solicitaba ayuda para la mujer. RECOPILAN INFORMACIÓN Agentes de la Policía Nacional acudieron posteriormente a la escena para realizar las primeras diligencias, verificar las condiciones del inmueble y recopilar información que permita reconstruir los momentos previos y posteriores al fatal incidente. Las autoridades deberán determinar si la caída se produjo accidentalmente o si existió la intervención de otra persona. Para ello, se vienen recogiendo testimonios de quiénes participaron en la fiesta y de otros posibles testigos, además de realizarse las pericias correspondientes. El cuerpo de Juliet Alisson Zambrano Fino fue trasladado a la morgue de Piura, donde se realizarán los procedimientos establecidos por ley. INVESTIGACIONES Mientras avanzan las investigaciones, el caso ha generado preocupación entre los vecinos de Las Casuarinas. La Policía busca establecer las circunstancias exactas de la muerte y, de corresponder, identificar a los responsables y determinar las responsabilidades que establezca la investigación.</t>
+          <t>En la carrera contra el tiempo para ejecutar las actividades que aminoren el impacto del Fenómeno El Niño (FEN) , la región se enfrenta a otro enemigo. Se trata del propio Estado y la complejidad de sus instituciones, procesos y competencias que hacen mucho más lenta la respuesta a la emergencia. PUEDES LEER ► Callao: joven de 20 años es asesinado a balazos en el distrito de Mi Perú “La situación de desorden que tenemos en el Estado es como decir que tenemos un monstruo de 10 cabezas. Está lo que maneja Veintiséis de Octubre, lo que maneja la Municipalidad de Piura o el Ministerio de Vivienda, cuando debería haber una sola cabeza en el control de inundaciones y de nuestras cuencas [Luego] tenemos el proyecto Alto Piura y el proyecto Chira Piura que manejan la jurisdicción de estas dos cuencas con el ANA (Autoridad Nacional del Agua) como ente rector. [También] tuvimos la Autoridad para la Reconstrucción con Cambios (ARCC) que evaluaba un plan maestro”, aseveró la senadora de Piura, Karla Schaefer. Otra muestra del problema de esta gran burocracia, señala, es que luego se creó la Autoridad Nacional de Infraestructura (ANIN) que también tiene fichas de intervención de diferentes puntos críticos. “Y esas benditas competencias que no te dejan [trabajar] y todos se mueren de miedo de firmar un documento por la Contraloría [...] Por ejemplo, el alcalde de Veintiséis de Octubre tiene una situación compleja con el dren Maldonado y que podría dejar incomunicado a 60 mil personas de un lado a otro. Se pidió el apoyo a Transportes, como una de las alternativas, que tiene puentes Baileys, aún esperamos respuesta. [...] Este es un tema que el decreto de urgencia nos debería dejar actuar y que no permitan que los empresarios, que hace dos semanas están esperando este documento, luego se vean entrampados” , consideró. Reunión Schaefer brindó estas declaraciones este martes en la primera sesión descentralizada del Consejo Directivo Descentralizado Macro Región Norte que agrupa a las empresas asociadas a la Confiep (Confederación Nacional de Instituciones Empresariales Privadas), que desean apoyar a las actividades de mitigación contra El Niño. Parte de este problema también fue expuesto por el presidente de la Confiep, Jorge Zapata , quien destacó que las empresas privadas podrían invertir unos 4 mil millones de sus impuestos en Piura bajo una modalidad abreviada de obras por impuestos Se trata de servicios por impuestos que todavía no existe porque debe aprobarse el decreto supremo para que las empresas privadas tengan marco legal para intervenir en Chutuque, cuencas ciegas u otros puntos críticos. “Pi ura cuenta con 4 mil 352 millones de soles bajo la modalidad de obras o servicios por impuestos. Tenemos la plata y no somos capaces de solucionar los temas. No es un tema de dinero y hace mucho tiempo lo venimos diciendo. Los privados ya están haciendo el esfuerzo necesario; ya hemos visto donaciones de varias empresas; la Sociedad Nacional de Minería está evaluando la apertura del canal de Chutuque, pero hay un detalle mínimo y que parece absurdo, sobre a quién se va a contratar para la información de la ficha técnica [de Chutuque]. Tenemos que ponernos de acuerdo en un detalle mínimo cuando tenemos 18 mil millones de soles por ejecutar”, destacó. Zapata mencionó esto en relación a la ficha técnica que hace falta para intervenir en los 6 kilómetros del canal Chutuque mediante explosivos. La ANA señala que no hay información, mientras que desde la Cámara de Comercio se indica que esta información la posee el ingeniero César Alvarado. Alvarado es el especialista y autor de la primera versión del Plan Integral de Manejo del Río Piura que contrató la desaparecida Autoridad para la Reconstrucción con Cambios (ARCC), la cual nació luego de la inundación del 2017.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/fiesta-termina-con-una-mujer-fallecida/</t>
+          <t>https://eltiempo.pe/local/monstruo-de-las-10-cabezas/</t>
         </is>
       </c>
     </row>
@@ -1309,21 +1348,21 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Piura: Dengue, una amenaza que sigue creciendo</t>
+          <t>Miniván queda al borde de un abismo en la carretera Canchaque -Huancabamba</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>El fenómeno El Niño aún no se manifiesta con fuertes lluvias en la región Piura, pero los casos de dengue ya superan las 8 mil personas infectadas . Un escenario peligroso de cara a lo que se viene en el verano que es cuando el zancudo transmisor de la enfermedad encuentra mejores condiciones para reproducirse. Asimismo, luego de vivir un año 2025 sin muertes por la enfermedad, en lo que va de este 2026 ya se han reportado cinco decesos por dengue. En tres casos, se confirmó la mortandad por dengue, mientras que los restantes siguen bajo investigación. Sobre el tema el médico epidemiólogo y exsubdirector de salud, César Guerrero, consideró que los casos actuales están fuera del promedio del canal endémico que se había previsto para esta época del año. “Hay más casos de lo que se esperaba en este año por lo cual se están tomando algunas acciones que podrían aumentar en el caso de finales de año, dependiendo de la intensidad de las lluvias y de los hábitos de las personas. Actualmente, se están reportando un promedio de 700 casos por semana. Además, hay otras subregiones que reportan curvas en ascenso” , sostuvo. Serotipo Asimismo, el especialista informó que también es posible un aumento de los casos graves tomando en cuenta que circulan los cuatro serotipos en la región. “Si yo he tenido una infección previa por un serotipo diferente al que me está dando actualmente, es más frecuente que el dengue actual sea más complicado. Si el año me dio dengue por el serotipo 1 y ahora te da dengue serotipo 3, puede hacer que la enfermedad sea más grave. [En el verano] podría ser que los casos que se presenten sean un poco más severos que los previos que tuvo”, afirmó. Agregó que en la actualidad están circulando dos tipos de serotipos del dengue completamente diferentes que están haciendo que se agrave la situación de salud de los piuranos. “Según las cifras de Diresa, el dengue con signos de alarma está en el orden del 15.9% de los enfermos de dengue y que ameritan hospitalización”, indicó. De otro lado, Guerrero agregó que con la proliferación del zancudo también aumenta el riesgo de propagación de otras enfermedades como el sika y chikungunya. A esto se sumarían las enfermedades digestivas por los problemas con el almacenamiento del agua potable durante las interrupciones del servicio. Leptospirosis, acecha y supera al 2025 Cabe indicar que de acuerdo a la sala situacional de la Dirección Regional de Salud (Diresa), los casos de leptospirosis ascienden a unss 1927 personas infectadas. La cifra genera preocupación porque dentro del mismo periodo del 2025, los reportes de los centros de salud solo habían contabilizado unos 341 casos de la bacteria. Cómo se sabe, las personas adquieren leptospirosis por el contacto con aguas empozadas y contaminadas con la bacteria que se encuentra en las deposiciones de los roedores. Este escenario podría complicarse con las lluvias de El Niño que generan acumulación de agua por falta sistema de drenaje. Del total de casos, la provincia de Sullana concentra el 33.7% de los casos, seguida por Morropón, Tambogrande y Chulucanas.</t>
+          <t>Unos 12 pasajeros se salvaron de caer a un abismo de aproximadamente 200 metros luego de que una miniván de una empresa de transporte sufriera un accidente en la carretera Canchaque-Huancabamba, en el sector Las Minas. Según información preliminar, la unidad terminó volcada y quedó peligrosamente cerca del precipicio, generando momentos de angustia entre los pasajeros, entre ellos algunos menores de edad, quienes temieron lo peor. Pese a la violencia del accidente, los ocupantes solo habrían sufrido algunos golpes, además del fuerte susto provocado por el incidente. Hasta el momento no se han reportado oficialmente personas con lesiones de consideración. EL EQUIPAJE El accidente también ocasionó la caída de algunos equipajes que eran transportados en la parte superior de la miniván, los cuales algunos habrían terminado en el fondo del abismo. De acuerdo con versiones preliminares, no se descarta que el vehículo haya sufrido algún desperfecto mecánico antes de producirse el accidente. Sin embargo, esta posibilidad deberá ser determinada mediante las investigaciones correspondientes. Asimismo, las autoridades realizan las diligencias para establecer las causas exactas del siniestro y determinar las condiciones en las que circulaba la unidad. Cabe mencionar que el hecho vuelve a poner en evidencia el peligro de transitar por esta vía, caracterizada por sus pronunciadas pendientes y zonas de profundo precipicio.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/piura-dengue-una-amenaza-que-sigue-creciendo/</t>
+          <t>https://eltiempo.pe/local/minivan-queda-al-borde-de-un-abismo-en-la-carretera-canchaque-huancabamba/</t>
         </is>
       </c>
     </row>
@@ -1338,17 +1377,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sechura: Exigen control de flotas por caída de la pota</t>
+          <t>Piura: Dengue, una amenaza que sigue creciendo</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>La pesquería del calamar gigante o pota enfrenta una severa crisis logística y de mercado en el litoral norteño. Henry Juárez, presidente del gremio de pescadores artesanales de Parachique, alertó sobre las graves consecuencias del incremento descontrolado de la flota, la cual pasó de 5,000 embarcaciones el año pasado a 9,000 en la presente temporada, debido a la migración de botes provenientes de otras pesquerías. PUEDES LEER ► Declaran en emergencia 5 penales, pero olvidan a Piura Esta sobreoferta de naves ha saturado la cadena de suministro local. La salida simultánea de la flota ha provocado un agudo desabastecimiento de hielo, elevando su costo hasta rangos de entre S/200 y S/250 por la alta demanda . A este difícil panorama se suma el encarecimiento del petróleo y de los servicios asociados. En el aspecto comercial, el dirigente denunció una fuerte especulación por parte de intermediarios en playa y una preocupante disparidad de precios en las plantas procesadoras. Mientras que en el sur del país las fábricas pagan S/3.00 por kilogramo, en el norte el valor descendió de S/3.00 a S/2.50. Ante esta situación, el gremio exige un sinceramiento de los precios para conocer los márgenes reales de ganancia de las plantas al exportar al extranjero. Como solución, Juárez plantea implementar un modelo de ordenamiento inspirado en Chile, donde se distribuyan topes de pesca a las embarcaciones de acuerdo con la capacidad real de procesamiento de las fábricas. Si bien, en Parachique, la asamblea comunal fiscaliza de forma interna los límites de descarga colocando inspectores a bordo de cada nave, esta medida no se puede replicar en muelles privados ni en Paita.</t>
+          <t>El fenómeno El Niño aún no se manifiesta con fuertes lluvias en la región Piura, pero los casos de dengue ya superan las 8 mil personas infectadas . Un escenario peligroso de cara a lo que se viene en el verano que es cuando el zancudo transmisor de la enfermedad encuentra mejores condiciones para reproducirse. Asimismo, luego de vivir un año 2025 sin muertes por la enfermedad, en lo que va de este 2026 ya se han reportado cinco decesos por dengue. En tres casos, se confirmó la mortandad por dengue, mientras que los restantes siguen bajo investigación. Sobre el tema el médico epidemiólogo y exsubdirector de salud, César Guerrero, consideró que los casos actuales están fuera del promedio del canal endémico que se había previsto para esta época del año. “Hay más casos de lo que se esperaba en este año por lo cual se están tomando algunas acciones que podrían aumentar en el caso de finales de año, dependiendo de la intensidad de las lluvias y de los hábitos de las personas. Actualmente, se están reportando un promedio de 700 casos por semana. Además, hay otras subregiones que reportan curvas en ascenso” , sostuvo. Serotipo Asimismo, el especialista informó que también es posible un aumento de los casos graves tomando en cuenta que circulan los cuatro serotipos en la región. “Si yo he tenido una infección previa por un serotipo diferente al que me está dando actualmente, es más frecuente que el dengue actual sea más complicado. Si el año me dio dengue por el serotipo 1 y ahora te da dengue serotipo 3, puede hacer que la enfermedad sea más grave. [En el verano] podría ser que los casos que se presenten sean un poco más severos que los previos que tuvo”, afirmó. Agregó que en la actualidad están circulando dos tipos de serotipos del dengue completamente diferentes que están haciendo que se agrave la situación de salud de los piuranos. “Según las cifras de Diresa, el dengue con signos de alarma está en el orden del 15.9% de los enfermos de dengue y que ameritan hospitalización”, indicó. De otro lado, Guerrero agregó que con la proliferación del zancudo también aumenta el riesgo de propagación de otras enfermedades como el sika y chikungunya. A esto se sumarían las enfermedades digestivas por los problemas con el almacenamiento del agua potable durante las interrupciones del servicio. Leptospirosis, acecha y supera al 2025 Cabe indicar que de acuerdo a la sala situacional de la Dirección Regional de Salud (Diresa), los casos de leptospirosis ascienden a unss 1927 personas infectadas. La cifra genera preocupación porque dentro del mismo periodo del 2025, los reportes de los centros de salud solo habían contabilizado unos 341 casos de la bacteria. Cómo se sabe, las personas adquieren leptospirosis por el contacto con aguas empozadas y contaminadas con la bacteria que se encuentra en las deposiciones de los roedores. Este escenario podría complicarse con las lluvias de El Niño que generan acumulación de agua por falta sistema de drenaje. Del total de casos, la provincia de Sullana concentra el 33.7% de los casos, seguida por Morropón, Tambogrande y Chulucanas.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://eltiempo.pe/local/sechura-exigen-control-de-flotas-por-caida-de-la-pota/</t>
+          <t>https://eltiempo.pe/local/piura-dengue-una-amenaza-que-sigue-creciendo/</t>
         </is>
       </c>
     </row>
@@ -1363,15 +1402,40 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>Sechura: Exigen control de flotas por caída de la pota</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>La pesquería del calamar gigante o pota enfrenta una severa crisis logística y de mercado en el litoral norteño. Henry Juárez, presidente del gremio de pescadores artesanales de Parachique, alertó sobre las graves consecuencias del incremento descontrolado de la flota, la cual pasó de 5,000 embarcaciones el año pasado a 9,000 en la presente temporada, debido a la migración de botes provenientes de otras pesquerías. PUEDES LEER ► Declaran en emergencia 5 penales, pero olvidan a Piura Esta sobreoferta de naves ha saturado la cadena de suministro local. La salida simultánea de la flota ha provocado un agudo desabastecimiento de hielo, elevando su costo hasta rangos de entre S/200 y S/250 por la alta demanda . A este difícil panorama se suma el encarecimiento del petróleo y de los servicios asociados. En el aspecto comercial, el dirigente denunció una fuerte especulación por parte de intermediarios en playa y una preocupante disparidad de precios en las plantas procesadoras. Mientras que en el sur del país las fábricas pagan S/3.00 por kilogramo, en el norte el valor descendió de S/3.00 a S/2.50. Ante esta situación, el gremio exige un sinceramiento de los precios para conocer los márgenes reales de ganancia de las plantas al exportar al extranjero. Como solución, Juárez plantea implementar un modelo de ordenamiento inspirado en Chile, donde se distribuyan topes de pesca a las embarcaciones de acuerdo con la capacidad real de procesamiento de las fábricas. Si bien, en Parachique, la asamblea comunal fiscaliza de forma interna los límites de descarga colocando inspectores a bordo de cada nave, esta medida no se puede replicar en muelles privados ni en Paita.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://eltiempo.pe/local/sechura-exigen-control-de-flotas-por-caida-de-la-pota/</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>El Tiempo</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
           <t>Piura: Defensoría advierte riesgo crítico de colapso de casonas ante próximas lluvias</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Para garantizar la seguridad de la ciudadanía y mitigar los impactos frente a la temporada de lluvias por el Fenómeno El Niño (FEN) 2026, personal de la Defensorial de Piura participó en la reunión de trabajo multisectorial para evaluar el estado situacional de las obras de infraestructura vial y los planes de contingencia vigentes en la provincia, convocada por la Segunda Fiscalía de Prevención del Delito del Ministerio Público. PUEDES LEER ► Tumbes: Detienen a adolescente y adulto luego de una persecución a balazos El encuentro contó con la participación de representantes de Corporación Diamantes Juvers SAC, Municipalidad de Castilla, equipo técnico de la EPS Grau, el supervisor de obras del centro de Piura y coordinadores de proyectos ejecutados en articulación con los gobiernos locales y el Gore. Durante la sesión, se solicitó los cronogramas y las condiciones de ejecución de las obras de pistas, veredas y drenaje pluvial que se desarrollan en la ciudad. Se enfatizó la necesidad de que las constructoras y entidades responsables adopten medidas correctivas inmediatas para evitar paralizaciones que dejen desprotegida a la infraestructura urbana ante las próximas precipitaciones.</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>https://eltiempo.pe/local/piura-defensoria-advierte-riesgo-critico-de-colapso-de-casonas-ante-proximas-lluvias/</t>
         </is>
